--- a/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,67 +656,67 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -726,41 +726,44 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>108800</v>
+        <v>104700</v>
       </c>
       <c r="E8" s="3">
-        <v>117600</v>
+        <v>342900</v>
       </c>
       <c r="F8" s="3">
-        <v>125400</v>
+        <v>114600</v>
       </c>
       <c r="G8" s="3">
-        <v>125800</v>
+        <v>122300</v>
       </c>
       <c r="H8" s="3">
-        <v>114900</v>
+        <v>122600</v>
       </c>
       <c r="I8" s="3">
-        <v>108000</v>
+        <v>315800</v>
       </c>
       <c r="J8" s="3">
+        <v>105200</v>
+      </c>
+      <c r="K8" s="3">
         <v>101100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>92200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>75700</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -770,41 +773,44 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>73400</v>
+        <v>69900</v>
       </c>
       <c r="E9" s="3">
-        <v>76900</v>
+        <v>299800</v>
       </c>
       <c r="F9" s="3">
-        <v>83900</v>
+        <v>75000</v>
       </c>
       <c r="G9" s="3">
-        <v>80400</v>
+        <v>81700</v>
       </c>
       <c r="H9" s="3">
-        <v>74800</v>
+        <v>156800</v>
       </c>
       <c r="I9" s="3">
-        <v>70200</v>
+        <v>280100</v>
       </c>
       <c r="J9" s="3">
+        <v>68400</v>
+      </c>
+      <c r="K9" s="3">
         <v>67700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>59500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>49700</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -814,41 +820,44 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>35400</v>
+        <v>34800</v>
       </c>
       <c r="E10" s="3">
-        <v>40600</v>
+        <v>43100</v>
       </c>
       <c r="F10" s="3">
-        <v>41600</v>
+        <v>39600</v>
       </c>
       <c r="G10" s="3">
-        <v>45400</v>
+        <v>40500</v>
       </c>
       <c r="H10" s="3">
-        <v>40200</v>
+        <v>-34200</v>
       </c>
       <c r="I10" s="3">
-        <v>37700</v>
+        <v>35700</v>
       </c>
       <c r="J10" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K10" s="3">
         <v>33500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>32700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>26000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -858,8 +867,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -876,8 +888,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -920,8 +933,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,41 +980,44 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>500</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>300</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>100</v>
+      </c>
+      <c r="J14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K14" s="3">
         <v>200</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="L14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J14" s="3">
-        <v>200</v>
-      </c>
-      <c r="K14" s="3">
-        <v>-300</v>
-      </c>
-      <c r="L14" s="3">
-        <v>300</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1008,8 +1027,11 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1052,8 +1074,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,41 +1092,42 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>93900</v>
       </c>
       <c r="E17" s="3">
-        <v>101600</v>
+        <v>296500</v>
       </c>
       <c r="F17" s="3">
-        <v>108100</v>
+        <v>99100</v>
       </c>
       <c r="G17" s="3">
-        <v>108000</v>
+        <v>105400</v>
       </c>
       <c r="H17" s="3">
-        <v>101700</v>
+        <v>105300</v>
       </c>
       <c r="I17" s="3">
-        <v>95300</v>
+        <v>278300</v>
       </c>
       <c r="J17" s="3">
+        <v>92900</v>
+      </c>
+      <c r="K17" s="3">
         <v>88500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>76300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>67900</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1111,41 +1137,44 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>10900</v>
       </c>
       <c r="E18" s="3">
-        <v>16000</v>
+        <v>46400</v>
       </c>
       <c r="F18" s="3">
+        <v>15500</v>
+      </c>
+      <c r="G18" s="3">
+        <v>16900</v>
+      </c>
+      <c r="H18" s="3">
         <v>17300</v>
       </c>
-      <c r="G18" s="3">
-        <v>17800</v>
-      </c>
-      <c r="H18" s="3">
-        <v>13300</v>
-      </c>
       <c r="I18" s="3">
-        <v>12700</v>
+        <v>37600</v>
       </c>
       <c r="J18" s="3">
+        <v>12300</v>
+      </c>
+      <c r="K18" s="3">
         <v>12600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>7900</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1155,8 +1184,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1173,41 +1205,42 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>2600</v>
       </c>
       <c r="E20" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F20" s="3">
+        <v>600</v>
+      </c>
+      <c r="G20" s="3">
         <v>700</v>
       </c>
-      <c r="F20" s="3">
-        <v>700</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-2700</v>
-      </c>
       <c r="H20" s="3">
-        <v>2200</v>
+        <v>7200</v>
       </c>
       <c r="I20" s="3">
-        <v>300</v>
+        <v>34800</v>
       </c>
       <c r="J20" s="3">
         <v>300</v>
       </c>
       <c r="K20" s="3">
+        <v>300</v>
+      </c>
+      <c r="L20" s="3">
         <v>5300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3500</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1217,38 +1250,41 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>17900</v>
       </c>
       <c r="E21" s="3">
-        <v>21400</v>
+        <v>77300</v>
       </c>
       <c r="F21" s="3">
-        <v>23100</v>
+        <v>20800</v>
       </c>
       <c r="G21" s="3">
-        <v>20700</v>
+        <v>22500</v>
       </c>
       <c r="H21" s="3">
-        <v>20300</v>
+        <v>30100</v>
       </c>
       <c r="I21" s="3">
-        <v>17900</v>
+        <v>85800</v>
       </c>
       <c r="J21" s="3">
+        <v>17500</v>
+      </c>
+      <c r="K21" s="3">
         <v>16900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>31000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1261,41 +1297,44 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>3</v>
+      <c r="D22" s="3">
+        <v>6100</v>
       </c>
       <c r="E22" s="3">
-        <v>4500</v>
+        <v>28500</v>
       </c>
       <c r="F22" s="3">
-        <v>4800</v>
+        <v>4300</v>
       </c>
       <c r="G22" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H22" s="3">
+        <v>13600</v>
+      </c>
+      <c r="I22" s="3">
+        <v>43200</v>
+      </c>
+      <c r="J22" s="3">
         <v>3800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="K22" s="3">
         <v>3700</v>
       </c>
-      <c r="I22" s="3">
-        <v>3900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>3700</v>
-      </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8100</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1305,41 +1344,44 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>10100</v>
+        <v>7400</v>
       </c>
       <c r="E23" s="3">
-        <v>12200</v>
+        <v>34600</v>
       </c>
       <c r="F23" s="3">
-        <v>13200</v>
+        <v>11900</v>
       </c>
       <c r="G23" s="3">
-        <v>11200</v>
+        <v>12800</v>
       </c>
       <c r="H23" s="3">
-        <v>11800</v>
+        <v>10900</v>
       </c>
       <c r="I23" s="3">
-        <v>9100</v>
+        <v>29200</v>
       </c>
       <c r="J23" s="3">
+        <v>8800</v>
+      </c>
+      <c r="K23" s="3">
         <v>9200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3400</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,41 +1391,44 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="E24" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F24" s="3">
         <v>2300</v>
       </c>
-      <c r="F24" s="3">
-        <v>2400</v>
-      </c>
       <c r="G24" s="3">
-        <v>5000</v>
+        <v>2300</v>
       </c>
       <c r="H24" s="3">
-        <v>3400</v>
+        <v>6500</v>
       </c>
       <c r="I24" s="3">
-        <v>3700</v>
+        <v>14500</v>
       </c>
       <c r="J24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K24" s="3">
         <v>3100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3800</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1393,8 +1438,11 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1437,41 +1485,44 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>4600</v>
       </c>
       <c r="E26" s="3">
-        <v>9800</v>
+        <v>22000</v>
       </c>
       <c r="F26" s="3">
-        <v>10800</v>
+        <v>9600</v>
       </c>
       <c r="G26" s="3">
-        <v>6200</v>
+        <v>10500</v>
       </c>
       <c r="H26" s="3">
-        <v>8400</v>
+        <v>4500</v>
       </c>
       <c r="I26" s="3">
-        <v>5300</v>
+        <v>14700</v>
       </c>
       <c r="J26" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K26" s="3">
         <v>6000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-400</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1481,41 +1532,44 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>4600</v>
       </c>
       <c r="E27" s="3">
-        <v>9800</v>
+        <v>22000</v>
       </c>
       <c r="F27" s="3">
-        <v>10800</v>
+        <v>9600</v>
       </c>
       <c r="G27" s="3">
-        <v>6200</v>
+        <v>10500</v>
       </c>
       <c r="H27" s="3">
-        <v>8400</v>
+        <v>4500</v>
       </c>
       <c r="I27" s="3">
-        <v>5300</v>
+        <v>14700</v>
       </c>
       <c r="J27" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K27" s="3">
         <v>6000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-400</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1525,8 +1579,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1569,8 +1626,11 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1613,8 +1673,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1657,8 +1720,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1701,41 +1767,44 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-2600</v>
       </c>
       <c r="E32" s="3">
+        <v>-16700</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="G32" s="3">
         <v>-700</v>
       </c>
-      <c r="F32" s="3">
-        <v>-700</v>
-      </c>
-      <c r="G32" s="3">
-        <v>2700</v>
-      </c>
       <c r="H32" s="3">
-        <v>-2200</v>
+        <v>-7200</v>
       </c>
       <c r="I32" s="3">
-        <v>-300</v>
+        <v>-34800</v>
       </c>
       <c r="J32" s="3">
         <v>-300</v>
       </c>
       <c r="K32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L32" s="3">
         <v>-5300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3500</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1745,41 +1814,44 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>4600</v>
       </c>
       <c r="E33" s="3">
-        <v>9800</v>
+        <v>22000</v>
       </c>
       <c r="F33" s="3">
-        <v>10800</v>
+        <v>9600</v>
       </c>
       <c r="G33" s="3">
-        <v>6200</v>
+        <v>10500</v>
       </c>
       <c r="H33" s="3">
-        <v>8400</v>
+        <v>4500</v>
       </c>
       <c r="I33" s="3">
-        <v>5300</v>
+        <v>14700</v>
       </c>
       <c r="J33" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K33" s="3">
         <v>6000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-400</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1789,8 +1861,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1833,41 +1908,44 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>4600</v>
       </c>
       <c r="E35" s="3">
-        <v>9800</v>
+        <v>22000</v>
       </c>
       <c r="F35" s="3">
-        <v>10800</v>
+        <v>9600</v>
       </c>
       <c r="G35" s="3">
-        <v>6200</v>
+        <v>10500</v>
       </c>
       <c r="H35" s="3">
-        <v>8400</v>
+        <v>4500</v>
       </c>
       <c r="I35" s="3">
-        <v>5300</v>
+        <v>14700</v>
       </c>
       <c r="J35" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K35" s="3">
         <v>6000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-400</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1877,46 +1955,49 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1926,8 +2007,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1944,8 +2028,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1962,41 +2047,42 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>40000</v>
+        <v>42400</v>
       </c>
       <c r="E41" s="3">
-        <v>18800</v>
+        <v>22600</v>
       </c>
       <c r="F41" s="3">
-        <v>31700</v>
+        <v>18300</v>
       </c>
       <c r="G41" s="3">
-        <v>26200</v>
+        <v>30900</v>
       </c>
       <c r="H41" s="3">
-        <v>16100</v>
+        <v>62700</v>
       </c>
       <c r="I41" s="3">
-        <v>12900</v>
+        <v>15700</v>
       </c>
       <c r="J41" s="3">
+        <v>12600</v>
+      </c>
+      <c r="K41" s="3">
         <v>13500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>27400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22800</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2006,38 +2092,41 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>8100</v>
+        <v>600</v>
       </c>
       <c r="E42" s="3">
-        <v>19300</v>
+        <v>24200</v>
       </c>
       <c r="F42" s="3">
-        <v>39400</v>
+        <v>18800</v>
       </c>
       <c r="G42" s="3">
-        <v>31800</v>
+        <v>38400</v>
       </c>
       <c r="H42" s="3">
-        <v>52500</v>
+        <v>31000</v>
       </c>
       <c r="I42" s="3">
-        <v>60600</v>
+        <v>51200</v>
       </c>
       <c r="J42" s="3">
+        <v>59000</v>
+      </c>
+      <c r="K42" s="3">
         <v>97000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>161200</v>
       </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2050,41 +2139,44 @@
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>141500</v>
+        <v>132400</v>
       </c>
       <c r="E43" s="3">
-        <v>147400</v>
+        <v>137900</v>
       </c>
       <c r="F43" s="3">
-        <v>142800</v>
+        <v>143700</v>
       </c>
       <c r="G43" s="3">
-        <v>150000</v>
+        <v>139100</v>
       </c>
       <c r="H43" s="3">
-        <v>143900</v>
+        <v>248800</v>
       </c>
       <c r="I43" s="3">
-        <v>137100</v>
+        <v>140200</v>
       </c>
       <c r="J43" s="3">
+        <v>133600</v>
+      </c>
+      <c r="K43" s="3">
         <v>111100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>98000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>96000</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2094,8 +2186,11 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2138,40 +2233,43 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>15600</v>
+        <v>7400</v>
       </c>
       <c r="E45" s="3">
-        <v>15300</v>
+        <v>15200</v>
       </c>
       <c r="F45" s="3">
-        <v>14800</v>
+        <v>14900</v>
       </c>
       <c r="G45" s="3">
-        <v>14200</v>
+        <v>14400</v>
       </c>
       <c r="H45" s="3">
-        <v>11900</v>
+        <v>13800</v>
       </c>
       <c r="I45" s="3">
-        <v>11100</v>
+        <v>11600</v>
       </c>
       <c r="J45" s="3">
+        <v>10800</v>
+      </c>
+      <c r="K45" s="3">
         <v>8500</v>
-      </c>
-      <c r="K45" s="3">
-        <v>6200</v>
       </c>
       <c r="L45" s="3">
         <v>6200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>6200</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
@@ -2182,41 +2280,44 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>205100</v>
+        <v>182800</v>
       </c>
       <c r="E46" s="3">
-        <v>200700</v>
+        <v>199900</v>
       </c>
       <c r="F46" s="3">
-        <v>228500</v>
+        <v>195700</v>
       </c>
       <c r="G46" s="3">
-        <v>222200</v>
+        <v>222800</v>
       </c>
       <c r="H46" s="3">
-        <v>224400</v>
+        <v>214700</v>
       </c>
       <c r="I46" s="3">
-        <v>221700</v>
+        <v>218700</v>
       </c>
       <c r="J46" s="3">
+        <v>216100</v>
+      </c>
+      <c r="K46" s="3">
         <v>230100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>292900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>125000</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2226,16 +2327,19 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="E47" s="3">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F47" s="3">
         <v>700</v>
@@ -2253,13 +2357,13 @@
         <v>700</v>
       </c>
       <c r="K47" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="L47" s="3">
         <v>600</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
+      <c r="M47" s="3">
+        <v>600</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>3</v>
@@ -2270,41 +2374,44 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>17500</v>
+        <v>15700</v>
       </c>
       <c r="E48" s="3">
-        <v>19200</v>
+        <v>17000</v>
       </c>
       <c r="F48" s="3">
-        <v>21100</v>
+        <v>18700</v>
       </c>
       <c r="G48" s="3">
-        <v>22900</v>
+        <v>20500</v>
       </c>
       <c r="H48" s="3">
-        <v>26900</v>
+        <v>33400</v>
       </c>
       <c r="I48" s="3">
-        <v>27800</v>
+        <v>26200</v>
       </c>
       <c r="J48" s="3">
+        <v>27000</v>
+      </c>
+      <c r="K48" s="3">
         <v>27500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26400</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2314,41 +2421,44 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>347700</v>
+        <v>334700</v>
       </c>
       <c r="E49" s="3">
-        <v>344200</v>
+        <v>338900</v>
       </c>
       <c r="F49" s="3">
-        <v>353500</v>
+        <v>335500</v>
       </c>
       <c r="G49" s="3">
-        <v>360000</v>
+        <v>344600</v>
       </c>
       <c r="H49" s="3">
-        <v>231100</v>
+        <v>702900</v>
       </c>
       <c r="I49" s="3">
-        <v>221700</v>
+        <v>225200</v>
       </c>
       <c r="J49" s="3">
+        <v>216100</v>
+      </c>
+      <c r="K49" s="3">
         <v>215900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>149100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>150200</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2358,8 +2468,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2402,8 +2515,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2446,41 +2562,44 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>15000</v>
+        <v>11200</v>
       </c>
       <c r="E52" s="3">
         <v>14600</v>
       </c>
       <c r="F52" s="3">
-        <v>16800</v>
+        <v>14200</v>
       </c>
       <c r="G52" s="3">
-        <v>16500</v>
+        <v>16400</v>
       </c>
       <c r="H52" s="3">
-        <v>16600</v>
+        <v>18500</v>
       </c>
       <c r="I52" s="3">
-        <v>14400</v>
+        <v>16100</v>
       </c>
       <c r="J52" s="3">
+        <v>14100</v>
+      </c>
+      <c r="K52" s="3">
         <v>11400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6300</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2490,8 +2609,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2534,41 +2656,44 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>586000</v>
+        <v>544500</v>
       </c>
       <c r="E54" s="3">
-        <v>579500</v>
+        <v>571100</v>
       </c>
       <c r="F54" s="3">
-        <v>620700</v>
+        <v>564800</v>
       </c>
       <c r="G54" s="3">
-        <v>622400</v>
+        <v>604900</v>
       </c>
       <c r="H54" s="3">
-        <v>499700</v>
+        <v>601900</v>
       </c>
       <c r="I54" s="3">
-        <v>486300</v>
+        <v>487000</v>
       </c>
       <c r="J54" s="3">
+        <v>474000</v>
+      </c>
+      <c r="K54" s="3">
         <v>485700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>476800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>308500</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2578,8 +2703,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2596,8 +2724,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2614,41 +2743,42 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F57" s="3">
         <v>12000</v>
       </c>
-      <c r="E57" s="3">
-        <v>12300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>19200</v>
-      </c>
       <c r="G57" s="3">
-        <v>21600</v>
+        <v>18700</v>
       </c>
       <c r="H57" s="3">
-        <v>18600</v>
+        <v>22100</v>
       </c>
       <c r="I57" s="3">
-        <v>28400</v>
+        <v>18100</v>
       </c>
       <c r="J57" s="3">
+        <v>27700</v>
+      </c>
+      <c r="K57" s="3">
         <v>27400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>24700</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2658,41 +2788,44 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>46200</v>
+        <v>22600</v>
       </c>
       <c r="E58" s="3">
-        <v>41200</v>
+        <v>45000</v>
       </c>
       <c r="F58" s="3">
-        <v>48000</v>
+        <v>40100</v>
       </c>
       <c r="G58" s="3">
-        <v>47600</v>
+        <v>46800</v>
       </c>
       <c r="H58" s="3">
-        <v>51900</v>
+        <v>47300</v>
       </c>
       <c r="I58" s="3">
-        <v>37700</v>
+        <v>50600</v>
       </c>
       <c r="J58" s="3">
+        <v>36800</v>
+      </c>
+      <c r="K58" s="3">
         <v>34700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>33200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>27900</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2702,41 +2835,44 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>69800</v>
+        <v>61600</v>
       </c>
       <c r="E59" s="3">
-        <v>66600</v>
+        <v>68000</v>
       </c>
       <c r="F59" s="3">
-        <v>83200</v>
+        <v>64900</v>
       </c>
       <c r="G59" s="3">
-        <v>86100</v>
+        <v>81100</v>
       </c>
       <c r="H59" s="3">
-        <v>83300</v>
+        <v>77700</v>
       </c>
       <c r="I59" s="3">
-        <v>72200</v>
+        <v>81200</v>
       </c>
       <c r="J59" s="3">
+        <v>70400</v>
+      </c>
+      <c r="K59" s="3">
         <v>72500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>61000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>56300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2746,41 +2882,44 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>128000</v>
+        <v>91200</v>
       </c>
       <c r="E60" s="3">
-        <v>120000</v>
+        <v>124700</v>
       </c>
       <c r="F60" s="3">
-        <v>150500</v>
+        <v>117000</v>
       </c>
       <c r="G60" s="3">
-        <v>155300</v>
+        <v>146700</v>
       </c>
       <c r="H60" s="3">
-        <v>153800</v>
+        <v>146300</v>
       </c>
       <c r="I60" s="3">
-        <v>138300</v>
+        <v>149900</v>
       </c>
       <c r="J60" s="3">
+        <v>134800</v>
+      </c>
+      <c r="K60" s="3">
         <v>134500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>110800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>109000</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2790,41 +2929,44 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>127600</v>
+        <v>123200</v>
       </c>
       <c r="E61" s="3">
-        <v>136300</v>
+        <v>124400</v>
       </c>
       <c r="F61" s="3">
-        <v>147000</v>
+        <v>132900</v>
       </c>
       <c r="G61" s="3">
-        <v>152800</v>
+        <v>143200</v>
       </c>
       <c r="H61" s="3">
-        <v>93300</v>
+        <v>151100</v>
       </c>
       <c r="I61" s="3">
-        <v>100700</v>
+        <v>90900</v>
       </c>
       <c r="J61" s="3">
+        <v>98200</v>
+      </c>
+      <c r="K61" s="3">
         <v>119100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>126000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>129600</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2834,41 +2976,44 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>35900</v>
+        <v>47200</v>
       </c>
       <c r="E62" s="3">
-        <v>35900</v>
+        <v>35000</v>
       </c>
       <c r="F62" s="3">
-        <v>38000</v>
+        <v>34900</v>
       </c>
       <c r="G62" s="3">
-        <v>39200</v>
+        <v>37000</v>
       </c>
       <c r="H62" s="3">
-        <v>25200</v>
+        <v>43100</v>
       </c>
       <c r="I62" s="3">
-        <v>28700</v>
+        <v>24600</v>
       </c>
       <c r="J62" s="3">
+        <v>28000</v>
+      </c>
+      <c r="K62" s="3">
         <v>24600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>20100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20000</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2878,8 +3023,11 @@
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2922,8 +3070,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2966,8 +3117,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3010,41 +3164,44 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>291500</v>
+        <v>261700</v>
       </c>
       <c r="E66" s="3">
-        <v>292200</v>
+        <v>284100</v>
       </c>
       <c r="F66" s="3">
-        <v>335500</v>
+        <v>284800</v>
       </c>
       <c r="G66" s="3">
-        <v>347200</v>
+        <v>327000</v>
       </c>
       <c r="H66" s="3">
-        <v>272400</v>
+        <v>339700</v>
       </c>
       <c r="I66" s="3">
-        <v>267800</v>
+        <v>265500</v>
       </c>
       <c r="J66" s="3">
+        <v>261000</v>
+      </c>
+      <c r="K66" s="3">
         <v>278200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>257000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>258500</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3054,8 +3211,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3072,8 +3232,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3116,8 +3277,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3160,8 +3324,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3204,8 +3371,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3248,41 +3418,44 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>126200</v>
+        <v>105900</v>
       </c>
       <c r="E72" s="3">
-        <v>117300</v>
+        <v>123000</v>
       </c>
       <c r="F72" s="3">
-        <v>105600</v>
+        <v>114300</v>
       </c>
       <c r="G72" s="3">
-        <v>93600</v>
+        <v>102900</v>
       </c>
       <c r="H72" s="3">
-        <v>51000</v>
+        <v>85200</v>
       </c>
       <c r="I72" s="3">
-        <v>42100</v>
+        <v>49700</v>
       </c>
       <c r="J72" s="3">
+        <v>41100</v>
+      </c>
+      <c r="K72" s="3">
         <v>35100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>27500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>31300</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3292,8 +3465,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3336,8 +3512,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3380,8 +3559,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3424,41 +3606,44 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>294500</v>
+        <v>282800</v>
       </c>
       <c r="E76" s="3">
-        <v>287200</v>
+        <v>287000</v>
       </c>
       <c r="F76" s="3">
-        <v>285200</v>
+        <v>279900</v>
       </c>
       <c r="G76" s="3">
-        <v>275200</v>
+        <v>278000</v>
       </c>
       <c r="H76" s="3">
-        <v>227300</v>
+        <v>262100</v>
       </c>
       <c r="I76" s="3">
-        <v>218500</v>
+        <v>221500</v>
       </c>
       <c r="J76" s="3">
+        <v>213000</v>
+      </c>
+      <c r="K76" s="3">
         <v>207400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>219900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>49900</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3468,8 +3653,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3512,46 +3700,49 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3561,41 +3752,44 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>4600</v>
       </c>
       <c r="E81" s="3">
-        <v>9800</v>
+        <v>22000</v>
       </c>
       <c r="F81" s="3">
-        <v>10800</v>
+        <v>9600</v>
       </c>
       <c r="G81" s="3">
-        <v>6200</v>
+        <v>10500</v>
       </c>
       <c r="H81" s="3">
-        <v>8400</v>
+        <v>4500</v>
       </c>
       <c r="I81" s="3">
-        <v>5300</v>
+        <v>14700</v>
       </c>
       <c r="J81" s="3">
+        <v>5200</v>
+      </c>
+      <c r="K81" s="3">
         <v>6000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-400</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3605,8 +3799,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3623,38 +3820,39 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4700</v>
+        <v>4500</v>
       </c>
       <c r="E83" s="3">
-        <v>4700</v>
+        <v>14200</v>
       </c>
       <c r="F83" s="3">
-        <v>5200</v>
+        <v>4600</v>
       </c>
       <c r="G83" s="3">
-        <v>5600</v>
+        <v>5000</v>
       </c>
       <c r="H83" s="3">
-        <v>4800</v>
+        <v>5500</v>
       </c>
       <c r="I83" s="3">
-        <v>5000</v>
+        <v>13500</v>
       </c>
       <c r="J83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K83" s="3">
         <v>4000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>9800</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3667,8 +3865,11 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3711,8 +3912,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3755,8 +3959,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3799,8 +4006,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3843,8 +4053,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3887,38 +4100,41 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>23800</v>
+        <v>23500</v>
       </c>
       <c r="E89" s="3">
-        <v>-6400</v>
+        <v>35600</v>
       </c>
       <c r="F89" s="3">
-        <v>19100</v>
+        <v>-6200</v>
       </c>
       <c r="G89" s="3">
-        <v>19900</v>
+        <v>18700</v>
       </c>
       <c r="H89" s="3">
-        <v>18300</v>
+        <v>19400</v>
       </c>
       <c r="I89" s="3">
-        <v>-15800</v>
+        <v>-12200</v>
       </c>
       <c r="J89" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-15000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>26700</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3931,8 +4147,11 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3949,8 +4168,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3984,8 +4204,8 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
       </c>
       <c r="O91" s="3" t="s">
         <v>3</v>
@@ -3993,8 +4213,11 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4037,8 +4260,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4081,38 +4307,41 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1900</v>
+        <v>5400</v>
       </c>
       <c r="E94" s="3">
-        <v>10600</v>
+        <v>7900</v>
       </c>
       <c r="F94" s="3">
+        <v>10300</v>
+      </c>
+      <c r="G94" s="3">
         <v>-600</v>
       </c>
-      <c r="G94" s="3">
-        <v>-53200</v>
-      </c>
       <c r="H94" s="3">
-        <v>-10100</v>
+        <v>-64300</v>
       </c>
       <c r="I94" s="3">
-        <v>27200</v>
+        <v>47800</v>
       </c>
       <c r="J94" s="3">
+        <v>26500</v>
+      </c>
+      <c r="K94" s="3">
         <v>19100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-304100</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4125,8 +4354,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4143,8 +4375,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4170,11 +4403,11 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-25400</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
@@ -4187,8 +4420,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4231,8 +4467,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4275,8 +4514,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4319,38 +4561,41 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-13400</v>
+        <v>-24800</v>
       </c>
       <c r="E100" s="3">
-        <v>-24900</v>
+        <v>-42000</v>
       </c>
       <c r="F100" s="3">
-        <v>-4800</v>
+        <v>-24300</v>
       </c>
       <c r="G100" s="3">
-        <v>41800</v>
+        <v>-4700</v>
       </c>
       <c r="H100" s="3">
-        <v>2500</v>
+        <v>40800</v>
       </c>
       <c r="I100" s="3">
-        <v>-15500</v>
+        <v>-20600</v>
       </c>
       <c r="J100" s="3">
+        <v>-15100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-8200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>277800</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4363,35 +4608,38 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
-        <v>-300</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G101" s="3">
+      <c r="J101" s="3">
         <v>-1600</v>
       </c>
-      <c r="H101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3300</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4407,38 +4655,41 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>3500</v>
       </c>
       <c r="E102" s="3">
-        <v>-21000</v>
+        <v>1700</v>
       </c>
       <c r="F102" s="3">
-        <v>13500</v>
+        <v>-20500</v>
       </c>
       <c r="G102" s="3">
-        <v>7000</v>
+        <v>13200</v>
       </c>
       <c r="H102" s="3">
-        <v>9800</v>
+        <v>6800</v>
       </c>
       <c r="I102" s="3">
-        <v>-5700</v>
+        <v>3200</v>
       </c>
       <c r="J102" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>300</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4449,6 +4700,9 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,70 +656,71 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -729,44 +730,47 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>104700</v>
+        <v>96700</v>
       </c>
       <c r="E8" s="3">
-        <v>342900</v>
+        <v>96600</v>
       </c>
       <c r="F8" s="3">
-        <v>114600</v>
+        <v>97800</v>
       </c>
       <c r="G8" s="3">
-        <v>122300</v>
+        <v>105600</v>
       </c>
       <c r="H8" s="3">
-        <v>122600</v>
+        <v>112700</v>
       </c>
       <c r="I8" s="3">
-        <v>315800</v>
+        <v>113000</v>
       </c>
       <c r="J8" s="3">
+        <v>103300</v>
+      </c>
+      <c r="K8" s="3">
         <v>105200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>101100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>92200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>75700</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -776,44 +780,47 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>69900</v>
+        <v>65800</v>
       </c>
       <c r="E9" s="3">
-        <v>299800</v>
+        <v>64500</v>
       </c>
       <c r="F9" s="3">
-        <v>75000</v>
+        <v>65900</v>
       </c>
       <c r="G9" s="3">
-        <v>81700</v>
+        <v>69100</v>
       </c>
       <c r="H9" s="3">
-        <v>156800</v>
+        <v>75400</v>
       </c>
       <c r="I9" s="3">
-        <v>280100</v>
+        <v>72300</v>
       </c>
       <c r="J9" s="3">
+        <v>67200</v>
+      </c>
+      <c r="K9" s="3">
         <v>68400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>67700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>59500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>49700</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -823,44 +830,47 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>34800</v>
+        <v>31000</v>
       </c>
       <c r="E10" s="3">
-        <v>43100</v>
+        <v>32100</v>
       </c>
       <c r="F10" s="3">
-        <v>39600</v>
+        <v>31800</v>
       </c>
       <c r="G10" s="3">
-        <v>40500</v>
+        <v>36500</v>
       </c>
       <c r="H10" s="3">
-        <v>-34200</v>
+        <v>37300</v>
       </c>
       <c r="I10" s="3">
-        <v>35700</v>
+        <v>40800</v>
       </c>
       <c r="J10" s="3">
+        <v>36100</v>
+      </c>
+      <c r="K10" s="3">
         <v>36800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>33500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>32700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>26000</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -870,8 +880,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -889,8 +902,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -936,8 +950,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,44 +1000,47 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-200</v>
       </c>
-      <c r="E14" s="3">
-        <v>500</v>
-      </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3">
         <v>-100</v>
       </c>
       <c r="K14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L14" s="3">
         <v>200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1030,8 +1050,11 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1077,8 +1100,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1093,44 +1119,45 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>93900</v>
+        <v>87200</v>
       </c>
       <c r="E17" s="3">
-        <v>296500</v>
+        <v>86500</v>
       </c>
       <c r="F17" s="3">
-        <v>99100</v>
+        <v>84900</v>
       </c>
       <c r="G17" s="3">
-        <v>105400</v>
+        <v>91300</v>
       </c>
       <c r="H17" s="3">
-        <v>105300</v>
+        <v>97200</v>
       </c>
       <c r="I17" s="3">
-        <v>278300</v>
+        <v>97000</v>
       </c>
       <c r="J17" s="3">
+        <v>91400</v>
+      </c>
+      <c r="K17" s="3">
         <v>92900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>88500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>76300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>67900</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1140,44 +1167,47 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10900</v>
+        <v>9500</v>
       </c>
       <c r="E18" s="3">
-        <v>46400</v>
+        <v>10000</v>
       </c>
       <c r="F18" s="3">
+        <v>12900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>14300</v>
+      </c>
+      <c r="H18" s="3">
         <v>15500</v>
       </c>
-      <c r="G18" s="3">
-        <v>16900</v>
-      </c>
-      <c r="H18" s="3">
-        <v>17300</v>
-      </c>
       <c r="I18" s="3">
-        <v>37600</v>
+        <v>16000</v>
       </c>
       <c r="J18" s="3">
+        <v>11900</v>
+      </c>
+      <c r="K18" s="3">
         <v>12300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>7900</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1187,8 +1217,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1206,44 +1239,45 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2600</v>
+        <v>1000</v>
       </c>
       <c r="E20" s="3">
-        <v>16700</v>
+        <v>300</v>
       </c>
       <c r="F20" s="3">
+        <v>100</v>
+      </c>
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
-        <v>700</v>
-      </c>
       <c r="H20" s="3">
-        <v>7200</v>
+        <v>400</v>
       </c>
       <c r="I20" s="3">
-        <v>34800</v>
+        <v>-2500</v>
       </c>
       <c r="J20" s="3">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="K20" s="3">
         <v>300</v>
       </c>
       <c r="L20" s="3">
+        <v>300</v>
+      </c>
+      <c r="M20" s="3">
         <v>5300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3500</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1253,41 +1287,44 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>17900</v>
+        <v>14500</v>
       </c>
       <c r="E21" s="3">
-        <v>77300</v>
+        <v>14400</v>
       </c>
       <c r="F21" s="3">
-        <v>20800</v>
+        <v>17200</v>
       </c>
       <c r="G21" s="3">
-        <v>22500</v>
+        <v>19200</v>
       </c>
       <c r="H21" s="3">
-        <v>30100</v>
+        <v>20600</v>
       </c>
       <c r="I21" s="3">
-        <v>85800</v>
+        <v>18600</v>
       </c>
       <c r="J21" s="3">
+        <v>18300</v>
+      </c>
+      <c r="K21" s="3">
         <v>17500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>16900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>31000</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1300,44 +1337,47 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>6100</v>
+        <v>3300</v>
       </c>
       <c r="E22" s="3">
-        <v>28500</v>
+        <v>3500</v>
       </c>
       <c r="F22" s="3">
-        <v>4300</v>
+        <v>3900</v>
       </c>
       <c r="G22" s="3">
-        <v>4700</v>
+        <v>4000</v>
       </c>
       <c r="H22" s="3">
-        <v>13600</v>
+        <v>4100</v>
       </c>
       <c r="I22" s="3">
-        <v>43200</v>
+        <v>3500</v>
       </c>
       <c r="J22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K22" s="3">
         <v>3800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8100</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1347,44 +1387,47 @@
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>7400</v>
+        <v>7200</v>
       </c>
       <c r="E23" s="3">
-        <v>34600</v>
+        <v>6800</v>
       </c>
       <c r="F23" s="3">
-        <v>11900</v>
+        <v>9100</v>
       </c>
       <c r="G23" s="3">
-        <v>12800</v>
+        <v>10900</v>
       </c>
       <c r="H23" s="3">
-        <v>10900</v>
+        <v>11800</v>
       </c>
       <c r="I23" s="3">
-        <v>29200</v>
+        <v>10100</v>
       </c>
       <c r="J23" s="3">
+        <v>10600</v>
+      </c>
+      <c r="K23" s="3">
         <v>8800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3400</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1394,44 +1437,47 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2800</v>
+        <v>3100</v>
       </c>
       <c r="E24" s="3">
-        <v>12600</v>
+        <v>7500</v>
       </c>
       <c r="F24" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="G24" s="3">
-        <v>2300</v>
+        <v>2100</v>
       </c>
       <c r="H24" s="3">
-        <v>6500</v>
+        <v>3800</v>
       </c>
       <c r="I24" s="3">
-        <v>14500</v>
+        <v>10100</v>
       </c>
       <c r="J24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K24" s="3">
         <v>3600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3800</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1441,8 +1487,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1488,44 +1537,47 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4600</v>
+        <v>4100</v>
       </c>
       <c r="E26" s="3">
-        <v>22000</v>
+        <v>-700</v>
       </c>
       <c r="F26" s="3">
-        <v>9600</v>
+        <v>6700</v>
       </c>
       <c r="G26" s="3">
-        <v>10500</v>
+        <v>8800</v>
       </c>
       <c r="H26" s="3">
-        <v>4500</v>
+        <v>8100</v>
       </c>
       <c r="I26" s="3">
-        <v>14700</v>
+        <v>0</v>
       </c>
       <c r="J26" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K26" s="3">
         <v>5200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>6000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-400</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1535,44 +1587,47 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4600</v>
+        <v>4100</v>
       </c>
       <c r="E27" s="3">
-        <v>22000</v>
+        <v>-700</v>
       </c>
       <c r="F27" s="3">
-        <v>9600</v>
+        <v>6700</v>
       </c>
       <c r="G27" s="3">
-        <v>10500</v>
+        <v>8800</v>
       </c>
       <c r="H27" s="3">
-        <v>4500</v>
+        <v>8100</v>
       </c>
       <c r="I27" s="3">
-        <v>14700</v>
+        <v>0</v>
       </c>
       <c r="J27" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K27" s="3">
         <v>5200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>6000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-400</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1582,8 +1637,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1629,8 +1687,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1676,8 +1737,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1723,8 +1787,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1770,44 +1837,47 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2600</v>
+        <v>-1000</v>
       </c>
       <c r="E32" s="3">
-        <v>-16700</v>
+        <v>-300</v>
       </c>
       <c r="F32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
-        <v>-700</v>
-      </c>
       <c r="H32" s="3">
-        <v>-7200</v>
+        <v>-400</v>
       </c>
       <c r="I32" s="3">
-        <v>-34800</v>
+        <v>2500</v>
       </c>
       <c r="J32" s="3">
-        <v>-300</v>
+        <v>-2000</v>
       </c>
       <c r="K32" s="3">
         <v>-300</v>
       </c>
       <c r="L32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M32" s="3">
         <v>-5300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3500</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1817,44 +1887,47 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4600</v>
+        <v>4100</v>
       </c>
       <c r="E33" s="3">
-        <v>22000</v>
+        <v>-700</v>
       </c>
       <c r="F33" s="3">
-        <v>9600</v>
+        <v>6700</v>
       </c>
       <c r="G33" s="3">
-        <v>10500</v>
+        <v>8800</v>
       </c>
       <c r="H33" s="3">
-        <v>4500</v>
+        <v>8100</v>
       </c>
       <c r="I33" s="3">
-        <v>14700</v>
+        <v>0</v>
       </c>
       <c r="J33" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K33" s="3">
         <v>5200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>6000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-400</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1864,8 +1937,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1911,44 +1987,47 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4600</v>
+        <v>4100</v>
       </c>
       <c r="E35" s="3">
-        <v>22000</v>
+        <v>-700</v>
       </c>
       <c r="F35" s="3">
-        <v>9600</v>
+        <v>6700</v>
       </c>
       <c r="G35" s="3">
-        <v>10500</v>
+        <v>8800</v>
       </c>
       <c r="H35" s="3">
-        <v>4500</v>
+        <v>8100</v>
       </c>
       <c r="I35" s="3">
-        <v>14700</v>
+        <v>0</v>
       </c>
       <c r="J35" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K35" s="3">
         <v>5200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>6000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-400</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1958,49 +2037,52 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2010,8 +2092,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2029,8 +2114,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2048,44 +2134,45 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>42400</v>
+        <v>66600</v>
       </c>
       <c r="E41" s="3">
-        <v>22600</v>
+        <v>11800</v>
       </c>
       <c r="F41" s="3">
-        <v>18300</v>
+        <v>20800</v>
       </c>
       <c r="G41" s="3">
-        <v>30900</v>
+        <v>16900</v>
       </c>
       <c r="H41" s="3">
-        <v>62700</v>
+        <v>28500</v>
       </c>
       <c r="I41" s="3">
-        <v>15700</v>
+        <v>23500</v>
       </c>
       <c r="J41" s="3">
+        <v>14500</v>
+      </c>
+      <c r="K41" s="3">
         <v>12600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>13500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>27400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22800</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2095,41 +2182,44 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>24200</v>
+        <v>27900</v>
       </c>
       <c r="F42" s="3">
-        <v>18800</v>
+        <v>22300</v>
       </c>
       <c r="G42" s="3">
-        <v>38400</v>
+        <v>17300</v>
       </c>
       <c r="H42" s="3">
-        <v>31000</v>
+        <v>35400</v>
       </c>
       <c r="I42" s="3">
-        <v>51200</v>
+        <v>28600</v>
       </c>
       <c r="J42" s="3">
+        <v>47200</v>
+      </c>
+      <c r="K42" s="3">
         <v>59000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>97000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>161200</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2142,44 +2232,47 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>111900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>122100</v>
+      </c>
+      <c r="F43" s="3">
+        <v>127100</v>
+      </c>
+      <c r="G43" s="3">
         <v>132400</v>
       </c>
-      <c r="E43" s="3">
-        <v>137900</v>
-      </c>
-      <c r="F43" s="3">
-        <v>143700</v>
-      </c>
-      <c r="G43" s="3">
-        <v>139100</v>
-      </c>
       <c r="H43" s="3">
-        <v>248800</v>
+        <v>128300</v>
       </c>
       <c r="I43" s="3">
-        <v>140200</v>
+        <v>136700</v>
       </c>
       <c r="J43" s="3">
+        <v>129300</v>
+      </c>
+      <c r="K43" s="3">
         <v>133600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>111100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>98000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>96000</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2189,8 +2282,11 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2236,43 +2332,46 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7400</v>
+        <v>6700</v>
       </c>
       <c r="E45" s="3">
-        <v>15200</v>
+        <v>6800</v>
       </c>
       <c r="F45" s="3">
-        <v>14900</v>
+        <v>14000</v>
       </c>
       <c r="G45" s="3">
-        <v>14400</v>
+        <v>13800</v>
       </c>
       <c r="H45" s="3">
-        <v>13800</v>
+        <v>13300</v>
       </c>
       <c r="I45" s="3">
-        <v>11600</v>
+        <v>12800</v>
       </c>
       <c r="J45" s="3">
+        <v>10700</v>
+      </c>
+      <c r="K45" s="3">
         <v>10800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>8500</v>
-      </c>
-      <c r="L45" s="3">
-        <v>6200</v>
       </c>
       <c r="M45" s="3">
         <v>6200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
+      <c r="N45" s="3">
+        <v>6200</v>
       </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
@@ -2283,44 +2382,47 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>182800</v>
+        <v>185100</v>
       </c>
       <c r="E46" s="3">
-        <v>199900</v>
+        <v>168500</v>
       </c>
       <c r="F46" s="3">
-        <v>195700</v>
+        <v>184300</v>
       </c>
       <c r="G46" s="3">
-        <v>222800</v>
+        <v>180400</v>
       </c>
       <c r="H46" s="3">
-        <v>214700</v>
+        <v>205400</v>
       </c>
       <c r="I46" s="3">
-        <v>218700</v>
+        <v>197900</v>
       </c>
       <c r="J46" s="3">
+        <v>201600</v>
+      </c>
+      <c r="K46" s="3">
         <v>216100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>230100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>292900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>125000</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2330,16 +2432,19 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>100</v>
+      </c>
+      <c r="E47" s="3">
         <v>200</v>
-      </c>
-      <c r="E47" s="3">
-        <v>700</v>
       </c>
       <c r="F47" s="3">
         <v>700</v>
@@ -2360,13 +2465,13 @@
         <v>700</v>
       </c>
       <c r="L47" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M47" s="3">
         <v>600</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
+      <c r="N47" s="3">
+        <v>600</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
@@ -2377,44 +2482,47 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="F48" s="3">
         <v>15700</v>
       </c>
-      <c r="E48" s="3">
-        <v>17000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>18700</v>
-      </c>
       <c r="G48" s="3">
-        <v>20500</v>
+        <v>17200</v>
       </c>
       <c r="H48" s="3">
-        <v>33400</v>
+        <v>18900</v>
       </c>
       <c r="I48" s="3">
-        <v>26200</v>
+        <v>20600</v>
       </c>
       <c r="J48" s="3">
+        <v>24200</v>
+      </c>
+      <c r="K48" s="3">
         <v>27000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>27500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26400</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2424,44 +2532,47 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>334700</v>
+        <v>312500</v>
       </c>
       <c r="E49" s="3">
-        <v>338900</v>
+        <v>308500</v>
       </c>
       <c r="F49" s="3">
-        <v>335500</v>
+        <v>312400</v>
       </c>
       <c r="G49" s="3">
-        <v>344600</v>
+        <v>309300</v>
       </c>
       <c r="H49" s="3">
-        <v>702900</v>
+        <v>317600</v>
       </c>
       <c r="I49" s="3">
-        <v>225200</v>
+        <v>324400</v>
       </c>
       <c r="J49" s="3">
+        <v>207600</v>
+      </c>
+      <c r="K49" s="3">
         <v>216100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>215900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>149100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>150200</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2471,8 +2582,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2518,8 +2632,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2565,44 +2682,47 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>10300</v>
+      </c>
+      <c r="F52" s="3">
+        <v>13500</v>
+      </c>
+      <c r="G52" s="3">
+        <v>13100</v>
+      </c>
+      <c r="H52" s="3">
+        <v>15100</v>
+      </c>
+      <c r="I52" s="3">
         <v>11200</v>
       </c>
-      <c r="E52" s="3">
-        <v>14600</v>
-      </c>
-      <c r="F52" s="3">
-        <v>14200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>16400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>18500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>16100</v>
-      </c>
       <c r="J52" s="3">
+        <v>14900</v>
+      </c>
+      <c r="K52" s="3">
         <v>14100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6300</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,8 +2732,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2659,44 +2782,47 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>544500</v>
+        <v>521500</v>
       </c>
       <c r="E54" s="3">
-        <v>571100</v>
+        <v>502000</v>
       </c>
       <c r="F54" s="3">
-        <v>564800</v>
+        <v>526500</v>
       </c>
       <c r="G54" s="3">
-        <v>604900</v>
+        <v>520700</v>
       </c>
       <c r="H54" s="3">
-        <v>601900</v>
+        <v>557700</v>
       </c>
       <c r="I54" s="3">
-        <v>487000</v>
+        <v>554800</v>
       </c>
       <c r="J54" s="3">
+        <v>449000</v>
+      </c>
+      <c r="K54" s="3">
         <v>474000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>485700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>476800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>308500</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2706,8 +2832,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2725,8 +2854,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2744,44 +2874,45 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>7000</v>
+        <v>24100</v>
       </c>
       <c r="E57" s="3">
-        <v>11700</v>
+        <v>6500</v>
       </c>
       <c r="F57" s="3">
-        <v>12000</v>
+        <v>10800</v>
       </c>
       <c r="G57" s="3">
-        <v>18700</v>
+        <v>11100</v>
       </c>
       <c r="H57" s="3">
-        <v>22100</v>
+        <v>17300</v>
       </c>
       <c r="I57" s="3">
-        <v>18100</v>
+        <v>20300</v>
       </c>
       <c r="J57" s="3">
+        <v>16700</v>
+      </c>
+      <c r="K57" s="3">
         <v>27700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>27400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>24700</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2791,44 +2922,47 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>22600</v>
+        <v>24700</v>
       </c>
       <c r="E58" s="3">
-        <v>45000</v>
+        <v>20800</v>
       </c>
       <c r="F58" s="3">
-        <v>40100</v>
+        <v>41500</v>
       </c>
       <c r="G58" s="3">
-        <v>46800</v>
+        <v>37000</v>
       </c>
       <c r="H58" s="3">
-        <v>47300</v>
+        <v>43200</v>
       </c>
       <c r="I58" s="3">
-        <v>50600</v>
+        <v>43600</v>
       </c>
       <c r="J58" s="3">
+        <v>46700</v>
+      </c>
+      <c r="K58" s="3">
         <v>36800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>34700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>33200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>27900</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2838,44 +2972,47 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>61600</v>
+        <v>53200</v>
       </c>
       <c r="E59" s="3">
-        <v>68000</v>
+        <v>56800</v>
       </c>
       <c r="F59" s="3">
-        <v>64900</v>
+        <v>62700</v>
       </c>
       <c r="G59" s="3">
-        <v>81100</v>
+        <v>59800</v>
       </c>
       <c r="H59" s="3">
-        <v>77700</v>
+        <v>74800</v>
       </c>
       <c r="I59" s="3">
-        <v>81200</v>
+        <v>77400</v>
       </c>
       <c r="J59" s="3">
+        <v>74800</v>
+      </c>
+      <c r="K59" s="3">
         <v>70400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>72500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>61000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>56300</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2885,44 +3022,47 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>91200</v>
+        <v>102000</v>
       </c>
       <c r="E60" s="3">
-        <v>124700</v>
+        <v>84100</v>
       </c>
       <c r="F60" s="3">
-        <v>117000</v>
+        <v>115000</v>
       </c>
       <c r="G60" s="3">
-        <v>146700</v>
+        <v>107900</v>
       </c>
       <c r="H60" s="3">
-        <v>146300</v>
+        <v>135200</v>
       </c>
       <c r="I60" s="3">
-        <v>149900</v>
+        <v>134800</v>
       </c>
       <c r="J60" s="3">
+        <v>138200</v>
+      </c>
+      <c r="K60" s="3">
         <v>134800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>134500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>110800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>109000</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2932,44 +3072,47 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>123200</v>
+        <v>122000</v>
       </c>
       <c r="E61" s="3">
-        <v>124400</v>
+        <v>113600</v>
       </c>
       <c r="F61" s="3">
-        <v>132900</v>
+        <v>114700</v>
       </c>
       <c r="G61" s="3">
-        <v>143200</v>
+        <v>122500</v>
       </c>
       <c r="H61" s="3">
-        <v>151100</v>
+        <v>132100</v>
       </c>
       <c r="I61" s="3">
-        <v>90900</v>
+        <v>139300</v>
       </c>
       <c r="J61" s="3">
+        <v>83800</v>
+      </c>
+      <c r="K61" s="3">
         <v>98200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>119100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>126000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>129600</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -2979,44 +3122,47 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>47200</v>
+        <v>29100</v>
       </c>
       <c r="E62" s="3">
-        <v>35000</v>
+        <v>43500</v>
       </c>
       <c r="F62" s="3">
-        <v>34900</v>
+        <v>32300</v>
       </c>
       <c r="G62" s="3">
-        <v>37000</v>
+        <v>32200</v>
       </c>
       <c r="H62" s="3">
-        <v>43100</v>
+        <v>34100</v>
       </c>
       <c r="I62" s="3">
+        <v>39100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>22700</v>
+      </c>
+      <c r="K62" s="3">
+        <v>28000</v>
+      </c>
+      <c r="L62" s="3">
         <v>24600</v>
       </c>
-      <c r="J62" s="3">
-        <v>28000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>24600</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20000</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,8 +3172,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3073,8 +3222,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3120,8 +3272,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3167,44 +3322,47 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>261700</v>
+        <v>253100</v>
       </c>
       <c r="E66" s="3">
-        <v>284100</v>
+        <v>241200</v>
       </c>
       <c r="F66" s="3">
-        <v>284800</v>
+        <v>261900</v>
       </c>
       <c r="G66" s="3">
-        <v>327000</v>
+        <v>262600</v>
       </c>
       <c r="H66" s="3">
-        <v>339700</v>
+        <v>301400</v>
       </c>
       <c r="I66" s="3">
-        <v>265500</v>
+        <v>313200</v>
       </c>
       <c r="J66" s="3">
+        <v>244700</v>
+      </c>
+      <c r="K66" s="3">
         <v>261000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>278200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>257000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>258500</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3214,8 +3372,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3233,8 +3394,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3280,8 +3442,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3327,8 +3492,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3374,8 +3542,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3421,44 +3592,47 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>105900</v>
+        <v>102300</v>
       </c>
       <c r="E72" s="3">
-        <v>123000</v>
+        <v>97600</v>
       </c>
       <c r="F72" s="3">
-        <v>114300</v>
+        <v>113400</v>
       </c>
       <c r="G72" s="3">
-        <v>102900</v>
+        <v>105400</v>
       </c>
       <c r="H72" s="3">
-        <v>85200</v>
+        <v>94800</v>
       </c>
       <c r="I72" s="3">
-        <v>49700</v>
+        <v>78500</v>
       </c>
       <c r="J72" s="3">
+        <v>45800</v>
+      </c>
+      <c r="K72" s="3">
         <v>41100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>35100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>27500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>31300</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3468,8 +3642,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3515,8 +3692,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3562,8 +3742,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3609,44 +3792,47 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>282800</v>
+        <v>268400</v>
       </c>
       <c r="E76" s="3">
-        <v>287000</v>
+        <v>260700</v>
       </c>
       <c r="F76" s="3">
-        <v>279900</v>
+        <v>264600</v>
       </c>
       <c r="G76" s="3">
-        <v>278000</v>
+        <v>258100</v>
       </c>
       <c r="H76" s="3">
-        <v>262100</v>
+        <v>256300</v>
       </c>
       <c r="I76" s="3">
-        <v>221500</v>
+        <v>241700</v>
       </c>
       <c r="J76" s="3">
+        <v>204200</v>
+      </c>
+      <c r="K76" s="3">
         <v>213000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>207400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>219900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>49900</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3656,8 +3842,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3703,49 +3892,52 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3755,44 +3947,47 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4600</v>
+        <v>4100</v>
       </c>
       <c r="E81" s="3">
-        <v>22000</v>
+        <v>-700</v>
       </c>
       <c r="F81" s="3">
-        <v>9600</v>
+        <v>6700</v>
       </c>
       <c r="G81" s="3">
-        <v>10500</v>
+        <v>8800</v>
       </c>
       <c r="H81" s="3">
-        <v>4500</v>
+        <v>8100</v>
       </c>
       <c r="I81" s="3">
-        <v>14700</v>
+        <v>0</v>
       </c>
       <c r="J81" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K81" s="3">
         <v>5200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>6000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-400</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3802,8 +3997,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3821,41 +4019,42 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4500</v>
+        <v>4000</v>
       </c>
       <c r="E83" s="3">
-        <v>14200</v>
+        <v>4100</v>
       </c>
       <c r="F83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G83" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H83" s="3">
         <v>4600</v>
       </c>
-      <c r="G83" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H83" s="3">
-        <v>5500</v>
-      </c>
       <c r="I83" s="3">
-        <v>13500</v>
+        <v>5100</v>
       </c>
       <c r="J83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K83" s="3">
         <v>4900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9800</v>
       </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3868,8 +4067,11 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3915,8 +4117,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3962,8 +4167,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4009,8 +4217,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4056,8 +4267,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4103,41 +4317,44 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>23500</v>
+        <v>22000</v>
       </c>
       <c r="E89" s="3">
-        <v>35600</v>
+        <v>21700</v>
       </c>
       <c r="F89" s="3">
-        <v>-6200</v>
+        <v>21400</v>
       </c>
       <c r="G89" s="3">
-        <v>18700</v>
+        <v>-5700</v>
       </c>
       <c r="H89" s="3">
-        <v>19400</v>
+        <v>17200</v>
       </c>
       <c r="I89" s="3">
-        <v>-12200</v>
+        <v>17900</v>
       </c>
       <c r="J89" s="3">
+        <v>16400</v>
+      </c>
+      <c r="K89" s="3">
         <v>-15400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-15000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>26700</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4150,8 +4367,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4169,29 +4389,30 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-15900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7200</v>
       </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
       <c r="J91" s="3">
         <v>0</v>
       </c>
@@ -4207,8 +4428,8 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4216,8 +4437,11 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4263,8 +4487,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4310,41 +4537,44 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>5400</v>
+        <v>-1500</v>
       </c>
       <c r="E94" s="3">
-        <v>7900</v>
+        <v>4900</v>
       </c>
       <c r="F94" s="3">
-        <v>10300</v>
+        <v>-1700</v>
       </c>
       <c r="G94" s="3">
-        <v>-600</v>
+        <v>9500</v>
       </c>
       <c r="H94" s="3">
-        <v>-64300</v>
+        <v>-500</v>
       </c>
       <c r="I94" s="3">
-        <v>47800</v>
+        <v>-59300</v>
       </c>
       <c r="J94" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K94" s="3">
         <v>26500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>19100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-304100</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4357,8 +4587,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4376,8 +4609,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4406,11 +4640,11 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-25400</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -4423,8 +4657,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4470,8 +4707,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4517,8 +4757,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4564,41 +4807,44 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-24800</v>
+        <v>6400</v>
       </c>
       <c r="E100" s="3">
-        <v>-42000</v>
+        <v>-22900</v>
       </c>
       <c r="F100" s="3">
-        <v>-24300</v>
+        <v>-12000</v>
       </c>
       <c r="G100" s="3">
-        <v>-4700</v>
+        <v>-22400</v>
       </c>
       <c r="H100" s="3">
-        <v>40800</v>
+        <v>-4300</v>
       </c>
       <c r="I100" s="3">
-        <v>-20600</v>
+        <v>37600</v>
       </c>
       <c r="J100" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K100" s="3">
         <v>-15100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-8200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>277800</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4611,38 +4857,41 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-600</v>
+        <v>500</v>
       </c>
       <c r="E101" s="3">
-        <v>100</v>
+        <v>-500</v>
       </c>
       <c r="F101" s="3">
+        <v>700</v>
+      </c>
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-800</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1600</v>
       </c>
-      <c r="I101" s="3">
-        <v>700</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3300</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4658,41 +4907,44 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3500</v>
+        <v>27500</v>
       </c>
       <c r="E102" s="3">
-        <v>1700</v>
+        <v>3200</v>
       </c>
       <c r="F102" s="3">
-        <v>-20500</v>
+        <v>8300</v>
       </c>
       <c r="G102" s="3">
-        <v>13200</v>
+        <v>-18900</v>
       </c>
       <c r="H102" s="3">
-        <v>6800</v>
+        <v>12200</v>
       </c>
       <c r="I102" s="3">
-        <v>3200</v>
+        <v>6300</v>
       </c>
       <c r="J102" s="3">
+        <v>8800</v>
+      </c>
+      <c r="K102" s="3">
         <v>-5500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>300</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4703,6 +4955,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,74 +656,75 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
@@ -733,47 +734,50 @@
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>96700</v>
+        <v>101700</v>
       </c>
       <c r="E8" s="3">
-        <v>96600</v>
+        <v>94100</v>
       </c>
       <c r="F8" s="3">
-        <v>97800</v>
+        <v>93900</v>
       </c>
       <c r="G8" s="3">
-        <v>105600</v>
+        <v>95100</v>
       </c>
       <c r="H8" s="3">
-        <v>112700</v>
+        <v>102800</v>
       </c>
       <c r="I8" s="3">
-        <v>113000</v>
+        <v>109600</v>
       </c>
       <c r="J8" s="3">
+        <v>110000</v>
+      </c>
+      <c r="K8" s="3">
         <v>103300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>105200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>101100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>92200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>75700</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
@@ -783,47 +787,50 @@
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>65800</v>
+        <v>66400</v>
       </c>
       <c r="E9" s="3">
-        <v>64500</v>
+        <v>64000</v>
       </c>
       <c r="F9" s="3">
-        <v>65900</v>
+        <v>62700</v>
       </c>
       <c r="G9" s="3">
-        <v>69100</v>
+        <v>64100</v>
       </c>
       <c r="H9" s="3">
-        <v>75400</v>
+        <v>67300</v>
       </c>
       <c r="I9" s="3">
-        <v>72300</v>
+        <v>73300</v>
       </c>
       <c r="J9" s="3">
+        <v>70300</v>
+      </c>
+      <c r="K9" s="3">
         <v>67200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>68400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>67700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>59500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>49700</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -833,47 +840,50 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>30100</v>
+      </c>
+      <c r="F10" s="3">
+        <v>31200</v>
+      </c>
+      <c r="G10" s="3">
         <v>31000</v>
       </c>
-      <c r="E10" s="3">
-        <v>32100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>31800</v>
-      </c>
-      <c r="G10" s="3">
-        <v>36500</v>
-      </c>
       <c r="H10" s="3">
-        <v>37300</v>
+        <v>35500</v>
       </c>
       <c r="I10" s="3">
-        <v>40800</v>
+        <v>36300</v>
       </c>
       <c r="J10" s="3">
+        <v>39700</v>
+      </c>
+      <c r="K10" s="3">
         <v>36100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>36800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>33500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>32700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>26000</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -883,8 +893,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,8 +916,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -953,8 +967,11 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1003,47 +1020,50 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>100</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>200</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3">
         <v>-100</v>
       </c>
       <c r="L14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M14" s="3">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1073,11 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1103,8 +1126,11 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1120,47 +1146,48 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>87200</v>
+        <v>87800</v>
       </c>
       <c r="E17" s="3">
-        <v>86500</v>
+        <v>84800</v>
       </c>
       <c r="F17" s="3">
-        <v>84900</v>
+        <v>84200</v>
       </c>
       <c r="G17" s="3">
-        <v>91300</v>
+        <v>82600</v>
       </c>
       <c r="H17" s="3">
-        <v>97200</v>
+        <v>88800</v>
       </c>
       <c r="I17" s="3">
-        <v>97000</v>
+        <v>94500</v>
       </c>
       <c r="J17" s="3">
+        <v>94400</v>
+      </c>
+      <c r="K17" s="3">
         <v>91400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>92900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>88500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>76300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>67900</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1170,47 +1197,50 @@
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>9500</v>
+        <v>13800</v>
       </c>
       <c r="E18" s="3">
-        <v>10000</v>
+        <v>9300</v>
       </c>
       <c r="F18" s="3">
-        <v>12900</v>
+        <v>9700</v>
       </c>
       <c r="G18" s="3">
-        <v>14300</v>
+        <v>12500</v>
       </c>
       <c r="H18" s="3">
-        <v>15500</v>
+        <v>13900</v>
       </c>
       <c r="I18" s="3">
-        <v>16000</v>
+        <v>15100</v>
       </c>
       <c r="J18" s="3">
+        <v>15600</v>
+      </c>
+      <c r="K18" s="3">
         <v>11900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>12300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>7900</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1220,8 +1250,11 @@
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1240,47 +1273,48 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>600</v>
-      </c>
       <c r="H20" s="3">
+        <v>500</v>
+      </c>
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
-        <v>-2500</v>
-      </c>
       <c r="J20" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K20" s="3">
         <v>2000</v>
-      </c>
-      <c r="K20" s="3">
-        <v>300</v>
       </c>
       <c r="L20" s="3">
         <v>300</v>
       </c>
       <c r="M20" s="3">
+        <v>300</v>
+      </c>
+      <c r="N20" s="3">
         <v>5300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3500</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1290,44 +1324,47 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>14500</v>
+        <v>19300</v>
       </c>
       <c r="E21" s="3">
-        <v>14400</v>
+        <v>14200</v>
       </c>
       <c r="F21" s="3">
-        <v>17200</v>
+        <v>14000</v>
       </c>
       <c r="G21" s="3">
-        <v>19200</v>
+        <v>16800</v>
       </c>
       <c r="H21" s="3">
-        <v>20600</v>
+        <v>18600</v>
       </c>
       <c r="I21" s="3">
-        <v>18600</v>
+        <v>20000</v>
       </c>
       <c r="J21" s="3">
+        <v>18100</v>
+      </c>
+      <c r="K21" s="3">
         <v>18300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>17500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>16900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>31000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1340,8 +1377,11 @@
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1349,38 +1389,38 @@
         <v>3300</v>
       </c>
       <c r="E22" s="3">
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="F22" s="3">
-        <v>3900</v>
+        <v>3400</v>
       </c>
       <c r="G22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="I22" s="3">
         <v>4000</v>
       </c>
-      <c r="H22" s="3">
-        <v>4100</v>
-      </c>
-      <c r="I22" s="3">
-        <v>3500</v>
-      </c>
       <c r="J22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K22" s="3">
         <v>3300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8100</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1390,47 +1430,50 @@
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>7200</v>
+        <v>11800</v>
       </c>
       <c r="E23" s="3">
-        <v>6800</v>
+        <v>7000</v>
       </c>
       <c r="F23" s="3">
-        <v>9100</v>
+        <v>6600</v>
       </c>
       <c r="G23" s="3">
-        <v>10900</v>
+        <v>8900</v>
       </c>
       <c r="H23" s="3">
-        <v>11800</v>
+        <v>10600</v>
       </c>
       <c r="I23" s="3">
-        <v>10100</v>
+        <v>11500</v>
       </c>
       <c r="J23" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K23" s="3">
         <v>10600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3400</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1440,47 +1483,50 @@
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F24" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I24" s="3">
+        <v>3700</v>
+      </c>
+      <c r="J24" s="3">
+        <v>9800</v>
+      </c>
+      <c r="K24" s="3">
         <v>3100</v>
       </c>
-      <c r="E24" s="3">
-        <v>7500</v>
-      </c>
-      <c r="F24" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G24" s="3">
-        <v>2100</v>
-      </c>
-      <c r="H24" s="3">
+      <c r="L24" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="N24" s="3">
+        <v>5400</v>
+      </c>
+      <c r="O24" s="3">
         <v>3800</v>
       </c>
-      <c r="I24" s="3">
-        <v>10100</v>
-      </c>
-      <c r="J24" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K24" s="3">
-        <v>3600</v>
-      </c>
-      <c r="L24" s="3">
-        <v>3100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>5400</v>
-      </c>
-      <c r="N24" s="3">
-        <v>3800</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1490,8 +1536,11 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1540,47 +1589,50 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>4100</v>
+        <v>8700</v>
       </c>
       <c r="E26" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F26" s="3">
         <v>-700</v>
       </c>
-      <c r="F26" s="3">
-        <v>6700</v>
-      </c>
       <c r="G26" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H26" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I26" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
+        <v>7500</v>
+      </c>
+      <c r="L26" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M26" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N26" s="3">
         <v>8800</v>
       </c>
-      <c r="H26" s="3">
-        <v>8100</v>
-      </c>
-      <c r="I26" s="3">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3">
-        <v>7500</v>
-      </c>
-      <c r="K26" s="3">
-        <v>5200</v>
-      </c>
-      <c r="L26" s="3">
-        <v>6000</v>
-      </c>
-      <c r="M26" s="3">
-        <v>8800</v>
-      </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-400</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1590,47 +1642,50 @@
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4100</v>
+        <v>8700</v>
       </c>
       <c r="E27" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F27" s="3">
         <v>-700</v>
       </c>
-      <c r="F27" s="3">
-        <v>6700</v>
-      </c>
       <c r="G27" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H27" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I27" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>7500</v>
+      </c>
+      <c r="L27" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M27" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N27" s="3">
         <v>8800</v>
       </c>
-      <c r="H27" s="3">
-        <v>8100</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
-        <v>7500</v>
-      </c>
-      <c r="K27" s="3">
-        <v>5200</v>
-      </c>
-      <c r="L27" s="3">
-        <v>6000</v>
-      </c>
-      <c r="M27" s="3">
-        <v>8800</v>
-      </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-400</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1640,8 +1695,11 @@
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1690,8 +1748,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1740,8 +1801,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1790,8 +1854,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1840,47 +1907,50 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>-600</v>
-      </c>
       <c r="H32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
-        <v>2500</v>
-      </c>
       <c r="J32" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-300</v>
       </c>
       <c r="L32" s="3">
         <v>-300</v>
       </c>
       <c r="M32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N32" s="3">
         <v>-5300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3500</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1890,47 +1960,50 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>4100</v>
+        <v>8700</v>
       </c>
       <c r="E33" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F33" s="3">
         <v>-700</v>
       </c>
-      <c r="F33" s="3">
-        <v>6700</v>
-      </c>
       <c r="G33" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H33" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I33" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
+        <v>7500</v>
+      </c>
+      <c r="L33" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M33" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N33" s="3">
         <v>8800</v>
       </c>
-      <c r="H33" s="3">
-        <v>8100</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3">
-        <v>7500</v>
-      </c>
-      <c r="K33" s="3">
-        <v>5200</v>
-      </c>
-      <c r="L33" s="3">
-        <v>6000</v>
-      </c>
-      <c r="M33" s="3">
-        <v>8800</v>
-      </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-400</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1940,8 +2013,11 @@
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1990,47 +2066,50 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>4100</v>
+        <v>8700</v>
       </c>
       <c r="E35" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F35" s="3">
         <v>-700</v>
       </c>
-      <c r="F35" s="3">
-        <v>6700</v>
-      </c>
       <c r="G35" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H35" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I35" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>7500</v>
+      </c>
+      <c r="L35" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M35" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N35" s="3">
         <v>8800</v>
       </c>
-      <c r="H35" s="3">
-        <v>8100</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3">
-        <v>7500</v>
-      </c>
-      <c r="K35" s="3">
-        <v>5200</v>
-      </c>
-      <c r="L35" s="3">
-        <v>6000</v>
-      </c>
-      <c r="M35" s="3">
-        <v>8800</v>
-      </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-400</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2040,52 +2119,55 @@
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2095,8 +2177,11 @@
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2115,8 +2200,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2135,47 +2221,48 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>66600</v>
+        <v>13900</v>
       </c>
       <c r="E41" s="3">
-        <v>11800</v>
+        <v>22300</v>
       </c>
       <c r="F41" s="3">
-        <v>20800</v>
+        <v>11400</v>
       </c>
       <c r="G41" s="3">
-        <v>16900</v>
+        <v>20300</v>
       </c>
       <c r="H41" s="3">
-        <v>28500</v>
+        <v>16400</v>
       </c>
       <c r="I41" s="3">
-        <v>23500</v>
+        <v>27700</v>
       </c>
       <c r="J41" s="3">
+        <v>22900</v>
+      </c>
+      <c r="K41" s="3">
         <v>14500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>13500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>27400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>22800</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2185,44 +2272,47 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>33700</v>
       </c>
       <c r="E42" s="3">
-        <v>27900</v>
+        <v>42400</v>
       </c>
       <c r="F42" s="3">
-        <v>22300</v>
+        <v>27200</v>
       </c>
       <c r="G42" s="3">
-        <v>17300</v>
+        <v>21700</v>
       </c>
       <c r="H42" s="3">
-        <v>35400</v>
+        <v>16800</v>
       </c>
       <c r="I42" s="3">
-        <v>28600</v>
+        <v>34400</v>
       </c>
       <c r="J42" s="3">
+        <v>27800</v>
+      </c>
+      <c r="K42" s="3">
         <v>47200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>59000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>97000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>161200</v>
       </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2235,47 +2325,50 @@
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>111900</v>
+        <v>135100</v>
       </c>
       <c r="E43" s="3">
-        <v>122100</v>
+        <v>108900</v>
       </c>
       <c r="F43" s="3">
-        <v>127100</v>
+        <v>118700</v>
       </c>
       <c r="G43" s="3">
-        <v>132400</v>
+        <v>123700</v>
       </c>
       <c r="H43" s="3">
-        <v>128300</v>
+        <v>128800</v>
       </c>
       <c r="I43" s="3">
-        <v>136700</v>
+        <v>124800</v>
       </c>
       <c r="J43" s="3">
+        <v>133000</v>
+      </c>
+      <c r="K43" s="3">
         <v>129300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>133600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>111100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>98000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>96000</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,8 +2378,11 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2335,46 +2431,49 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>6700</v>
+        <v>11700</v>
       </c>
       <c r="E45" s="3">
-        <v>6800</v>
+        <v>6500</v>
       </c>
       <c r="F45" s="3">
-        <v>14000</v>
+        <v>6600</v>
       </c>
       <c r="G45" s="3">
-        <v>13800</v>
+        <v>13600</v>
       </c>
       <c r="H45" s="3">
-        <v>13300</v>
+        <v>13400</v>
       </c>
       <c r="I45" s="3">
-        <v>12800</v>
+        <v>12900</v>
       </c>
       <c r="J45" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K45" s="3">
         <v>10700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8500</v>
-      </c>
-      <c r="M45" s="3">
-        <v>6200</v>
       </c>
       <c r="N45" s="3">
         <v>6200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
+      <c r="O45" s="3">
+        <v>6200</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
@@ -2385,47 +2484,50 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>185100</v>
+        <v>194400</v>
       </c>
       <c r="E46" s="3">
-        <v>168500</v>
+        <v>180100</v>
       </c>
       <c r="F46" s="3">
-        <v>184300</v>
+        <v>163900</v>
       </c>
       <c r="G46" s="3">
-        <v>180400</v>
+        <v>179300</v>
       </c>
       <c r="H46" s="3">
-        <v>205400</v>
+        <v>175500</v>
       </c>
       <c r="I46" s="3">
-        <v>197900</v>
+        <v>199800</v>
       </c>
       <c r="J46" s="3">
+        <v>192500</v>
+      </c>
+      <c r="K46" s="3">
         <v>201600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>216100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>230100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>292900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>125000</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2537,11 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2444,10 +2549,10 @@
         <v>100</v>
       </c>
       <c r="E47" s="3">
+        <v>100</v>
+      </c>
+      <c r="F47" s="3">
         <v>200</v>
-      </c>
-      <c r="F47" s="3">
-        <v>700</v>
       </c>
       <c r="G47" s="3">
         <v>700</v>
@@ -2468,13 +2573,13 @@
         <v>700</v>
       </c>
       <c r="M47" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="N47" s="3">
         <v>600</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
+      <c r="O47" s="3">
+        <v>600</v>
       </c>
       <c r="P47" s="3" t="s">
         <v>3</v>
@@ -2485,47 +2590,50 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>13100</v>
+        <v>15800</v>
       </c>
       <c r="E48" s="3">
-        <v>14500</v>
+        <v>12700</v>
       </c>
       <c r="F48" s="3">
-        <v>15700</v>
+        <v>14100</v>
       </c>
       <c r="G48" s="3">
-        <v>17200</v>
+        <v>15300</v>
       </c>
       <c r="H48" s="3">
-        <v>18900</v>
+        <v>16700</v>
       </c>
       <c r="I48" s="3">
-        <v>20600</v>
+        <v>18400</v>
       </c>
       <c r="J48" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K48" s="3">
         <v>24200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>27000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>27500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26400</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2535,47 +2643,50 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>312500</v>
+        <v>322200</v>
       </c>
       <c r="E49" s="3">
-        <v>308500</v>
+        <v>304000</v>
       </c>
       <c r="F49" s="3">
-        <v>312400</v>
+        <v>300100</v>
       </c>
       <c r="G49" s="3">
-        <v>309300</v>
+        <v>303900</v>
       </c>
       <c r="H49" s="3">
-        <v>317600</v>
+        <v>300900</v>
       </c>
       <c r="I49" s="3">
-        <v>324400</v>
+        <v>309000</v>
       </c>
       <c r="J49" s="3">
+        <v>315600</v>
+      </c>
+      <c r="K49" s="3">
         <v>207600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>216100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>215900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>149100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>150200</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2585,8 +2696,11 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2635,8 +2749,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2685,47 +2802,50 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10700</v>
+        <v>7800</v>
       </c>
       <c r="E52" s="3">
-        <v>10300</v>
+        <v>10400</v>
       </c>
       <c r="F52" s="3">
-        <v>13500</v>
+        <v>10000</v>
       </c>
       <c r="G52" s="3">
         <v>13100</v>
       </c>
       <c r="H52" s="3">
-        <v>15100</v>
+        <v>12700</v>
       </c>
       <c r="I52" s="3">
-        <v>11200</v>
+        <v>14700</v>
       </c>
       <c r="J52" s="3">
+        <v>10900</v>
+      </c>
+      <c r="K52" s="3">
         <v>14900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6300</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2735,8 +2855,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2785,47 +2908,50 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>521500</v>
+        <v>540300</v>
       </c>
       <c r="E54" s="3">
-        <v>502000</v>
+        <v>507300</v>
       </c>
       <c r="F54" s="3">
-        <v>526500</v>
+        <v>488300</v>
       </c>
       <c r="G54" s="3">
-        <v>520700</v>
+        <v>512200</v>
       </c>
       <c r="H54" s="3">
-        <v>557700</v>
+        <v>506500</v>
       </c>
       <c r="I54" s="3">
-        <v>554800</v>
+        <v>542500</v>
       </c>
       <c r="J54" s="3">
+        <v>539700</v>
+      </c>
+      <c r="K54" s="3">
         <v>449000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>474000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>485700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>476800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>308500</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,8 +2961,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2855,8 +2984,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2875,47 +3005,48 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>24100</v>
+        <v>25500</v>
       </c>
       <c r="E57" s="3">
-        <v>6500</v>
+        <v>23400</v>
       </c>
       <c r="F57" s="3">
+        <v>6300</v>
+      </c>
+      <c r="G57" s="3">
+        <v>10500</v>
+      </c>
+      <c r="H57" s="3">
         <v>10800</v>
       </c>
-      <c r="G57" s="3">
-        <v>11100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>17300</v>
-      </c>
       <c r="I57" s="3">
-        <v>20300</v>
+        <v>16800</v>
       </c>
       <c r="J57" s="3">
+        <v>19800</v>
+      </c>
+      <c r="K57" s="3">
         <v>16700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>27700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>24700</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2925,47 +3056,50 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>24700</v>
+        <v>32800</v>
       </c>
       <c r="E58" s="3">
-        <v>20800</v>
+        <v>26800</v>
       </c>
       <c r="F58" s="3">
-        <v>41500</v>
+        <v>23500</v>
       </c>
       <c r="G58" s="3">
-        <v>37000</v>
+        <v>43800</v>
       </c>
       <c r="H58" s="3">
-        <v>43200</v>
+        <v>39600</v>
       </c>
       <c r="I58" s="3">
-        <v>43600</v>
+        <v>45600</v>
       </c>
       <c r="J58" s="3">
+        <v>46300</v>
+      </c>
+      <c r="K58" s="3">
         <v>46700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>36800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>34700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>33200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>27900</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2975,47 +3109,50 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>53200</v>
+        <v>49600</v>
       </c>
       <c r="E59" s="3">
-        <v>56800</v>
+        <v>48900</v>
       </c>
       <c r="F59" s="3">
-        <v>62700</v>
+        <v>52100</v>
       </c>
       <c r="G59" s="3">
-        <v>59800</v>
+        <v>57600</v>
       </c>
       <c r="H59" s="3">
+        <v>54600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>69200</v>
+      </c>
+      <c r="J59" s="3">
+        <v>71400</v>
+      </c>
+      <c r="K59" s="3">
         <v>74800</v>
       </c>
-      <c r="I59" s="3">
-        <v>77400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>74800</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>70400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>72500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>61000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>56300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3025,47 +3162,50 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>102000</v>
+        <v>107800</v>
       </c>
       <c r="E60" s="3">
-        <v>84100</v>
+        <v>99200</v>
       </c>
       <c r="F60" s="3">
-        <v>115000</v>
+        <v>81800</v>
       </c>
       <c r="G60" s="3">
-        <v>107900</v>
+        <v>111800</v>
       </c>
       <c r="H60" s="3">
-        <v>135200</v>
+        <v>104900</v>
       </c>
       <c r="I60" s="3">
+        <v>131500</v>
+      </c>
+      <c r="J60" s="3">
+        <v>131200</v>
+      </c>
+      <c r="K60" s="3">
+        <v>138200</v>
+      </c>
+      <c r="L60" s="3">
         <v>134800</v>
       </c>
-      <c r="J60" s="3">
-        <v>138200</v>
-      </c>
-      <c r="K60" s="3">
-        <v>134800</v>
-      </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>134500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>110800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>109000</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3075,47 +3215,50 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>122000</v>
+        <v>126600</v>
       </c>
       <c r="E61" s="3">
-        <v>113600</v>
+        <v>123200</v>
       </c>
       <c r="F61" s="3">
-        <v>114700</v>
+        <v>115300</v>
       </c>
       <c r="G61" s="3">
-        <v>122500</v>
+        <v>116900</v>
       </c>
       <c r="H61" s="3">
-        <v>132100</v>
+        <v>125000</v>
       </c>
       <c r="I61" s="3">
-        <v>139300</v>
+        <v>135100</v>
       </c>
       <c r="J61" s="3">
+        <v>142900</v>
+      </c>
+      <c r="K61" s="3">
         <v>83800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>98200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>119100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>126000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>129600</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3125,47 +3268,50 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>29100</v>
+        <v>24600</v>
       </c>
       <c r="E62" s="3">
-        <v>43500</v>
+        <v>23800</v>
       </c>
       <c r="F62" s="3">
-        <v>32300</v>
+        <v>37500</v>
       </c>
       <c r="G62" s="3">
-        <v>32200</v>
+        <v>26000</v>
       </c>
       <c r="H62" s="3">
-        <v>34100</v>
+        <v>25500</v>
       </c>
       <c r="I62" s="3">
-        <v>39100</v>
+        <v>26500</v>
       </c>
       <c r="J62" s="3">
+        <v>30600</v>
+      </c>
+      <c r="K62" s="3">
         <v>22700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>24600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>20100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3175,8 +3321,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3225,8 +3374,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3275,8 +3427,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3325,47 +3480,50 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>253100</v>
+        <v>259000</v>
       </c>
       <c r="E66" s="3">
-        <v>241200</v>
+        <v>246200</v>
       </c>
       <c r="F66" s="3">
-        <v>261900</v>
+        <v>234700</v>
       </c>
       <c r="G66" s="3">
-        <v>262600</v>
+        <v>254800</v>
       </c>
       <c r="H66" s="3">
-        <v>301400</v>
+        <v>255400</v>
       </c>
       <c r="I66" s="3">
-        <v>313200</v>
+        <v>293200</v>
       </c>
       <c r="J66" s="3">
+        <v>304600</v>
+      </c>
+      <c r="K66" s="3">
         <v>244700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>261000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>278200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>257000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>258500</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3375,8 +3533,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3395,8 +3556,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3445,8 +3607,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3495,8 +3660,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3545,8 +3713,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3595,47 +3766,50 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>102300</v>
+        <v>109400</v>
       </c>
       <c r="E72" s="3">
-        <v>97600</v>
+        <v>99500</v>
       </c>
       <c r="F72" s="3">
-        <v>113400</v>
+        <v>95000</v>
       </c>
       <c r="G72" s="3">
-        <v>105400</v>
+        <v>110300</v>
       </c>
       <c r="H72" s="3">
-        <v>94800</v>
+        <v>102500</v>
       </c>
       <c r="I72" s="3">
-        <v>78500</v>
+        <v>92300</v>
       </c>
       <c r="J72" s="3">
+        <v>76400</v>
+      </c>
+      <c r="K72" s="3">
         <v>45800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>41100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>35100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>27500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>31300</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3819,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3695,8 +3872,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3745,8 +3925,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3795,47 +3978,50 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>268400</v>
+        <v>281300</v>
       </c>
       <c r="E76" s="3">
-        <v>260700</v>
+        <v>261100</v>
       </c>
       <c r="F76" s="3">
-        <v>264600</v>
+        <v>253600</v>
       </c>
       <c r="G76" s="3">
-        <v>258100</v>
+        <v>257400</v>
       </c>
       <c r="H76" s="3">
-        <v>256300</v>
+        <v>251000</v>
       </c>
       <c r="I76" s="3">
-        <v>241700</v>
+        <v>249300</v>
       </c>
       <c r="J76" s="3">
+        <v>235100</v>
+      </c>
+      <c r="K76" s="3">
         <v>204200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>213000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>207400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>219900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>49900</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3845,8 +4031,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3895,52 +4084,55 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3950,47 +4142,50 @@
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>4100</v>
+        <v>8700</v>
       </c>
       <c r="E81" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F81" s="3">
         <v>-700</v>
       </c>
-      <c r="F81" s="3">
-        <v>6700</v>
-      </c>
       <c r="G81" s="3">
+        <v>6500</v>
+      </c>
+      <c r="H81" s="3">
+        <v>7000</v>
+      </c>
+      <c r="I81" s="3">
+        <v>7800</v>
+      </c>
+      <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
+        <v>7500</v>
+      </c>
+      <c r="L81" s="3">
+        <v>5200</v>
+      </c>
+      <c r="M81" s="3">
+        <v>6000</v>
+      </c>
+      <c r="N81" s="3">
         <v>8800</v>
       </c>
-      <c r="H81" s="3">
-        <v>8100</v>
-      </c>
-      <c r="I81" s="3">
-        <v>0</v>
-      </c>
-      <c r="J81" s="3">
-        <v>7500</v>
-      </c>
-      <c r="K81" s="3">
-        <v>5200</v>
-      </c>
-      <c r="L81" s="3">
-        <v>6000</v>
-      </c>
-      <c r="M81" s="3">
-        <v>8800</v>
-      </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-400</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4000,8 +4195,11 @@
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4020,44 +4218,45 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F83" s="3">
         <v>4000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>4100</v>
       </c>
-      <c r="F83" s="3">
-        <v>4200</v>
-      </c>
-      <c r="G83" s="3">
-        <v>4300</v>
-      </c>
       <c r="H83" s="3">
-        <v>4600</v>
+        <v>4100</v>
       </c>
       <c r="I83" s="3">
-        <v>5100</v>
+        <v>4500</v>
       </c>
       <c r="J83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K83" s="3">
         <v>4400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9800</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4070,8 +4269,11 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4120,8 +4322,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4170,8 +4375,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4220,8 +4428,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4270,8 +4481,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4320,44 +4534,47 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>22000</v>
+        <v>-4100</v>
       </c>
       <c r="E89" s="3">
-        <v>21700</v>
+        <v>21400</v>
       </c>
       <c r="F89" s="3">
-        <v>21400</v>
+        <v>21100</v>
       </c>
       <c r="G89" s="3">
-        <v>-5700</v>
+        <v>20800</v>
       </c>
       <c r="H89" s="3">
-        <v>17200</v>
+        <v>-5600</v>
       </c>
       <c r="I89" s="3">
-        <v>17900</v>
+        <v>16700</v>
       </c>
       <c r="J89" s="3">
+        <v>17400</v>
+      </c>
+      <c r="K89" s="3">
         <v>16400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-15400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>26700</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4370,8 +4587,11 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4390,32 +4610,33 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7200</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
-      </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
@@ -4431,8 +4652,8 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
@@ -4440,8 +4661,11 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4490,8 +4714,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4540,44 +4767,47 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1500</v>
+        <v>-2400</v>
       </c>
       <c r="E94" s="3">
-        <v>4900</v>
+        <v>-1400</v>
       </c>
       <c r="F94" s="3">
+        <v>4800</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1700</v>
       </c>
-      <c r="G94" s="3">
-        <v>9500</v>
-      </c>
       <c r="H94" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
-        <v>-59300</v>
-      </c>
       <c r="J94" s="3">
+        <v>-57700</v>
+      </c>
+      <c r="K94" s="3">
         <v>2400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>26500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>19100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-304100</v>
       </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4590,8 +4820,11 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4610,8 +4843,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4643,11 +4877,11 @@
         <v>0</v>
       </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-25400</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
@@ -4660,8 +4894,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4710,8 +4947,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4760,8 +5000,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4810,44 +5053,47 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>6400</v>
+        <v>-10500</v>
       </c>
       <c r="E100" s="3">
-        <v>-22900</v>
+        <v>6200</v>
       </c>
       <c r="F100" s="3">
-        <v>-12000</v>
+        <v>-22300</v>
       </c>
       <c r="G100" s="3">
-        <v>-22400</v>
+        <v>-11700</v>
       </c>
       <c r="H100" s="3">
-        <v>-4300</v>
+        <v>-21800</v>
       </c>
       <c r="I100" s="3">
-        <v>37600</v>
+        <v>-4200</v>
       </c>
       <c r="J100" s="3">
+        <v>36600</v>
+      </c>
+      <c r="K100" s="3">
         <v>2300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-15100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-8200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>277800</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4860,41 +5106,44 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-500</v>
       </c>
-      <c r="F101" s="3">
-        <v>700</v>
-      </c>
       <c r="G101" s="3">
+        <v>600</v>
+      </c>
+      <c r="H101" s="3">
         <v>-300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3300</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4910,44 +5159,47 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>27500</v>
+        <v>-17200</v>
       </c>
       <c r="E102" s="3">
-        <v>3200</v>
+        <v>26700</v>
       </c>
       <c r="F102" s="3">
-        <v>8300</v>
+        <v>3100</v>
       </c>
       <c r="G102" s="3">
-        <v>-18900</v>
+        <v>8100</v>
       </c>
       <c r="H102" s="3">
-        <v>12200</v>
+        <v>-18400</v>
       </c>
       <c r="I102" s="3">
-        <v>6300</v>
+        <v>11800</v>
       </c>
       <c r="J102" s="3">
+        <v>6100</v>
+      </c>
+      <c r="K102" s="3">
         <v>8800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>300</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4958,6 +5210,9 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,78 +656,79 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -737,50 +738,53 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>101700</v>
+        <v>114300</v>
       </c>
       <c r="E8" s="3">
-        <v>94100</v>
+        <v>101900</v>
       </c>
       <c r="F8" s="3">
-        <v>93900</v>
+        <v>104400</v>
       </c>
       <c r="G8" s="3">
-        <v>95100</v>
+        <v>107700</v>
       </c>
       <c r="H8" s="3">
-        <v>102800</v>
+        <v>105900</v>
       </c>
       <c r="I8" s="3">
-        <v>109600</v>
+        <v>118600</v>
       </c>
       <c r="J8" s="3">
+        <v>120500</v>
+      </c>
+      <c r="K8" s="3">
         <v>110000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>103300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>105200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>101100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>92200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>75700</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
@@ -790,50 +794,53 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>66400</v>
+        <v>74600</v>
       </c>
       <c r="E9" s="3">
-        <v>64000</v>
+        <v>66600</v>
       </c>
       <c r="F9" s="3">
-        <v>62700</v>
+        <v>71000</v>
       </c>
       <c r="G9" s="3">
-        <v>64100</v>
+        <v>71900</v>
       </c>
       <c r="H9" s="3">
-        <v>67300</v>
+        <v>71400</v>
       </c>
       <c r="I9" s="3">
-        <v>73300</v>
+        <v>77600</v>
       </c>
       <c r="J9" s="3">
+        <v>80500</v>
+      </c>
+      <c r="K9" s="3">
         <v>70300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>67200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>68400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>67700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>59500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>49700</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -843,50 +850,53 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>35200</v>
+        <v>39600</v>
       </c>
       <c r="E10" s="3">
-        <v>30100</v>
+        <v>35300</v>
       </c>
       <c r="F10" s="3">
-        <v>31200</v>
+        <v>33400</v>
       </c>
       <c r="G10" s="3">
-        <v>31000</v>
+        <v>35800</v>
       </c>
       <c r="H10" s="3">
-        <v>35500</v>
+        <v>34500</v>
       </c>
       <c r="I10" s="3">
-        <v>36300</v>
+        <v>41000</v>
       </c>
       <c r="J10" s="3">
+        <v>39900</v>
+      </c>
+      <c r="K10" s="3">
         <v>39700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>36100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>36800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>33500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>32700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>26000</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -896,8 +906,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -917,8 +930,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -928,11 +942,11 @@
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
+      <c r="F12" s="3">
+        <v>200</v>
+      </c>
+      <c r="G12" s="3">
+        <v>100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -940,8 +954,8 @@
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
+      <c r="J12" s="3">
+        <v>100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
@@ -970,8 +984,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1023,50 +1040,53 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>100</v>
-      </c>
-      <c r="E14" s="3">
-        <v>300</v>
-      </c>
-      <c r="F14" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G14" s="3">
-        <v>200</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>300</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3">
         <v>-100</v>
       </c>
       <c r="M14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N14" s="3">
         <v>200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1076,31 +1096,34 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>7300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>3400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>3600</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1129,8 +1152,11 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1147,50 +1173,51 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>87800</v>
+        <v>99900</v>
       </c>
       <c r="E17" s="3">
-        <v>84800</v>
+        <v>88000</v>
       </c>
       <c r="F17" s="3">
-        <v>84200</v>
+        <v>94100</v>
       </c>
       <c r="G17" s="3">
-        <v>82600</v>
+        <v>96500</v>
       </c>
       <c r="H17" s="3">
-        <v>88800</v>
+        <v>92000</v>
       </c>
       <c r="I17" s="3">
-        <v>94500</v>
+        <v>102500</v>
       </c>
       <c r="J17" s="3">
+        <v>103900</v>
+      </c>
+      <c r="K17" s="3">
         <v>94400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>91400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>92900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>88500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>76300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>67900</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1200,50 +1227,53 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>13800</v>
+        <v>14400</v>
       </c>
       <c r="E18" s="3">
-        <v>9300</v>
+        <v>13900</v>
       </c>
       <c r="F18" s="3">
-        <v>9700</v>
+        <v>10300</v>
       </c>
       <c r="G18" s="3">
-        <v>12500</v>
+        <v>11200</v>
       </c>
       <c r="H18" s="3">
         <v>13900</v>
       </c>
       <c r="I18" s="3">
-        <v>15100</v>
+        <v>16100</v>
       </c>
       <c r="J18" s="3">
+        <v>16600</v>
+      </c>
+      <c r="K18" s="3">
         <v>15600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>7900</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1253,8 +1283,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1274,50 +1307,51 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="E20" s="3">
-        <v>1000</v>
+        <v>-900</v>
       </c>
       <c r="F20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G20" s="3">
         <v>300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
+        <v>200</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3">
-        <v>500</v>
-      </c>
-      <c r="I20" s="3">
-        <v>400</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>300</v>
       </c>
       <c r="M20" s="3">
         <v>300</v>
       </c>
       <c r="N20" s="3">
+        <v>300</v>
+      </c>
+      <c r="O20" s="3">
         <v>5300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>3500</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1327,47 +1361,50 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>19300</v>
+        <v>16400</v>
       </c>
       <c r="E21" s="3">
-        <v>14200</v>
+        <v>17500</v>
       </c>
       <c r="F21" s="3">
-        <v>14000</v>
+        <v>13800</v>
       </c>
       <c r="G21" s="3">
-        <v>16800</v>
+        <v>14100</v>
       </c>
       <c r="H21" s="3">
-        <v>18600</v>
+        <v>21000</v>
       </c>
       <c r="I21" s="3">
-        <v>20000</v>
+        <v>19800</v>
       </c>
       <c r="J21" s="3">
+        <v>20100</v>
+      </c>
+      <c r="K21" s="3">
         <v>18100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>18300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>17500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>16900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>31000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1380,50 +1417,53 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3500</v>
+      </c>
+      <c r="G22" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="I22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="J22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L22" s="3">
         <v>3300</v>
       </c>
-      <c r="E22" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F22" s="3">
-        <v>3400</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="M22" s="3">
         <v>3800</v>
       </c>
-      <c r="H22" s="3">
-        <v>3800</v>
-      </c>
-      <c r="I22" s="3">
-        <v>4000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>3400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>3300</v>
-      </c>
-      <c r="L22" s="3">
-        <v>3800</v>
-      </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>8100</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1433,50 +1473,53 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E23" s="3">
         <v>11800</v>
       </c>
-      <c r="E23" s="3">
-        <v>7000</v>
-      </c>
       <c r="F23" s="3">
-        <v>6600</v>
+        <v>7800</v>
       </c>
       <c r="G23" s="3">
-        <v>8900</v>
+        <v>7600</v>
       </c>
       <c r="H23" s="3">
+        <v>9900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>12300</v>
+      </c>
+      <c r="J23" s="3">
+        <v>12700</v>
+      </c>
+      <c r="K23" s="3">
+        <v>9800</v>
+      </c>
+      <c r="L23" s="3">
         <v>10600</v>
       </c>
-      <c r="I23" s="3">
-        <v>11500</v>
-      </c>
-      <c r="J23" s="3">
-        <v>9800</v>
-      </c>
-      <c r="K23" s="3">
-        <v>10600</v>
-      </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3400</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1486,50 +1529,53 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>3000</v>
+        <v>5400</v>
       </c>
       <c r="E24" s="3">
         <v>3000</v>
       </c>
       <c r="F24" s="3">
-        <v>7300</v>
+        <v>3400</v>
       </c>
       <c r="G24" s="3">
-        <v>2400</v>
+        <v>8400</v>
       </c>
       <c r="H24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I24" s="3">
+        <v>4200</v>
+      </c>
+      <c r="J24" s="3">
+        <v>4000</v>
+      </c>
+      <c r="K24" s="3">
+        <v>9800</v>
+      </c>
+      <c r="L24" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M24" s="3">
         <v>3600</v>
       </c>
-      <c r="I24" s="3">
-        <v>3700</v>
-      </c>
-      <c r="J24" s="3">
-        <v>9800</v>
-      </c>
-      <c r="K24" s="3">
+      <c r="N24" s="3">
         <v>3100</v>
       </c>
-      <c r="L24" s="3">
-        <v>3600</v>
-      </c>
-      <c r="M24" s="3">
-        <v>3100</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3800</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,8 +1585,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1592,50 +1641,53 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E26" s="3">
         <v>8700</v>
       </c>
-      <c r="E26" s="3">
-        <v>4000</v>
-      </c>
       <c r="F26" s="3">
-        <v>-700</v>
+        <v>4500</v>
       </c>
       <c r="G26" s="3">
-        <v>6500</v>
+        <v>-800</v>
       </c>
       <c r="H26" s="3">
-        <v>7000</v>
+        <v>5400</v>
       </c>
       <c r="I26" s="3">
-        <v>7800</v>
+        <v>8100</v>
       </c>
       <c r="J26" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>7500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>6000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-400</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1645,50 +1697,53 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E27" s="3">
         <v>8700</v>
       </c>
-      <c r="E27" s="3">
-        <v>4000</v>
-      </c>
       <c r="F27" s="3">
-        <v>-700</v>
+        <v>4500</v>
       </c>
       <c r="G27" s="3">
-        <v>6500</v>
+        <v>-800</v>
       </c>
       <c r="H27" s="3">
-        <v>7000</v>
+        <v>5400</v>
       </c>
       <c r="I27" s="3">
-        <v>7800</v>
+        <v>8100</v>
       </c>
       <c r="J27" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>7500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-400</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,8 +1753,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1751,8 +1809,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1804,8 +1865,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1857,8 +1921,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1910,50 +1977,53 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1200</v>
+        <v>-800</v>
       </c>
       <c r="E32" s="3">
-        <v>-1000</v>
+        <v>900</v>
       </c>
       <c r="F32" s="3">
+        <v>500</v>
+      </c>
+      <c r="G32" s="3">
         <v>-300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I32" s="3">
+        <v>300</v>
+      </c>
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-300</v>
       </c>
       <c r="M32" s="3">
         <v>-300</v>
       </c>
       <c r="N32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O32" s="3">
         <v>-5300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-3500</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1963,50 +2033,53 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E33" s="3">
         <v>8700</v>
       </c>
-      <c r="E33" s="3">
-        <v>4000</v>
-      </c>
       <c r="F33" s="3">
-        <v>-700</v>
+        <v>4500</v>
       </c>
       <c r="G33" s="3">
-        <v>6500</v>
+        <v>-800</v>
       </c>
       <c r="H33" s="3">
-        <v>7000</v>
+        <v>5400</v>
       </c>
       <c r="I33" s="3">
-        <v>7800</v>
+        <v>8100</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>7500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-400</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2016,8 +2089,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2069,50 +2145,53 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E35" s="3">
         <v>8700</v>
       </c>
-      <c r="E35" s="3">
-        <v>4000</v>
-      </c>
       <c r="F35" s="3">
-        <v>-700</v>
+        <v>4500</v>
       </c>
       <c r="G35" s="3">
-        <v>6500</v>
+        <v>-800</v>
       </c>
       <c r="H35" s="3">
-        <v>7000</v>
+        <v>5400</v>
       </c>
       <c r="I35" s="3">
-        <v>7800</v>
+        <v>8100</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>7500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-400</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,55 +2201,58 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2180,8 +2262,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2201,8 +2286,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2222,50 +2308,51 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>13900</v>
+        <v>70400</v>
       </c>
       <c r="E41" s="3">
-        <v>22300</v>
+        <v>47700</v>
       </c>
       <c r="F41" s="3">
-        <v>11400</v>
+        <v>71800</v>
       </c>
       <c r="G41" s="3">
-        <v>20300</v>
+        <v>43600</v>
       </c>
       <c r="H41" s="3">
-        <v>16400</v>
+        <v>38900</v>
       </c>
       <c r="I41" s="3">
-        <v>27700</v>
+        <v>31000</v>
       </c>
       <c r="J41" s="3">
+        <v>49700</v>
+      </c>
+      <c r="K41" s="3">
         <v>22900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>12600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>13500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>27400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22800</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2275,47 +2362,50 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>33700</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>42400</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>27200</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>21700</v>
+        <v>700</v>
       </c>
       <c r="H42" s="3">
-        <v>16800</v>
+        <v>7800</v>
       </c>
       <c r="I42" s="3">
-        <v>34400</v>
+        <v>7400</v>
       </c>
       <c r="J42" s="3">
+        <v>18500</v>
+      </c>
+      <c r="K42" s="3">
         <v>27800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>47200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>59000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>97000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>161200</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2328,50 +2418,53 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>135100</v>
+        <v>136600</v>
       </c>
       <c r="E43" s="3">
-        <v>108900</v>
+        <v>135400</v>
       </c>
       <c r="F43" s="3">
-        <v>118700</v>
+        <v>120800</v>
       </c>
       <c r="G43" s="3">
-        <v>123700</v>
+        <v>136200</v>
       </c>
       <c r="H43" s="3">
-        <v>128800</v>
+        <v>137800</v>
       </c>
       <c r="I43" s="3">
-        <v>124800</v>
+        <v>148700</v>
       </c>
       <c r="J43" s="3">
+        <v>137100</v>
+      </c>
+      <c r="K43" s="3">
         <v>133000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>129300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>133600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>111100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>98000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>96000</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2381,31 +2474,34 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2434,49 +2530,52 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>11700</v>
+        <v>5700</v>
       </c>
       <c r="E45" s="3">
-        <v>6500</v>
+        <v>7600</v>
       </c>
       <c r="F45" s="3">
-        <v>6600</v>
+        <v>7200</v>
       </c>
       <c r="G45" s="3">
-        <v>13600</v>
+        <v>7600</v>
       </c>
       <c r="H45" s="3">
-        <v>13400</v>
+        <v>15200</v>
       </c>
       <c r="I45" s="3">
-        <v>12900</v>
+        <v>15400</v>
       </c>
       <c r="J45" s="3">
+        <v>14200</v>
+      </c>
+      <c r="K45" s="3">
         <v>12400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>8500</v>
-      </c>
-      <c r="N45" s="3">
-        <v>6200</v>
       </c>
       <c r="O45" s="3">
         <v>6200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
+      <c r="P45" s="3">
+        <v>6200</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
@@ -2487,50 +2586,53 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>194400</v>
+        <v>217300</v>
       </c>
       <c r="E46" s="3">
-        <v>180100</v>
+        <v>194900</v>
       </c>
       <c r="F46" s="3">
-        <v>163900</v>
+        <v>199800</v>
       </c>
       <c r="G46" s="3">
-        <v>179300</v>
+        <v>188000</v>
       </c>
       <c r="H46" s="3">
-        <v>175500</v>
+        <v>199700</v>
       </c>
       <c r="I46" s="3">
-        <v>199800</v>
+        <v>202500</v>
       </c>
       <c r="J46" s="3">
+        <v>219500</v>
+      </c>
+      <c r="K46" s="3">
         <v>192500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>201600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>216100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>230100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>292900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>125000</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2540,31 +2642,34 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>100</v>
-      </c>
-      <c r="E47" s="3">
-        <v>100</v>
-      </c>
-      <c r="F47" s="3">
-        <v>200</v>
-      </c>
-      <c r="G47" s="3">
-        <v>700</v>
-      </c>
-      <c r="H47" s="3">
-        <v>700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>700</v>
-      </c>
-      <c r="J47" s="3">
-        <v>700</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>700</v>
@@ -2576,13 +2681,13 @@
         <v>700</v>
       </c>
       <c r="N47" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="O47" s="3">
         <v>600</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
+      <c r="P47" s="3">
+        <v>600</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
@@ -2593,50 +2698,53 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E48" s="3">
         <v>15800</v>
-      </c>
-      <c r="E48" s="3">
-        <v>12700</v>
       </c>
       <c r="F48" s="3">
         <v>14100</v>
       </c>
       <c r="G48" s="3">
-        <v>15300</v>
+        <v>16100</v>
       </c>
       <c r="H48" s="3">
-        <v>16700</v>
+        <v>17000</v>
       </c>
       <c r="I48" s="3">
-        <v>18400</v>
+        <v>19300</v>
       </c>
       <c r="J48" s="3">
+        <v>20200</v>
+      </c>
+      <c r="K48" s="3">
         <v>20000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>24200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>27000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26400</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,50 +2754,53 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>322200</v>
+        <v>328200</v>
       </c>
       <c r="E49" s="3">
-        <v>304000</v>
+        <v>322900</v>
       </c>
       <c r="F49" s="3">
-        <v>300100</v>
+        <v>337200</v>
       </c>
       <c r="G49" s="3">
-        <v>303900</v>
+        <v>344100</v>
       </c>
       <c r="H49" s="3">
-        <v>300900</v>
+        <v>338600</v>
       </c>
       <c r="I49" s="3">
-        <v>309000</v>
+        <v>347200</v>
       </c>
       <c r="J49" s="3">
+        <v>339500</v>
+      </c>
+      <c r="K49" s="3">
         <v>315600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>207600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>216100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>215900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>149100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>150200</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2699,8 +2810,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2752,8 +2866,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2805,50 +2922,53 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F52" s="3">
         <v>7800</v>
       </c>
-      <c r="E52" s="3">
-        <v>10400</v>
-      </c>
-      <c r="F52" s="3">
-        <v>10000</v>
-      </c>
       <c r="G52" s="3">
-        <v>13100</v>
+        <v>7900</v>
       </c>
       <c r="H52" s="3">
-        <v>12700</v>
+        <v>9400</v>
       </c>
       <c r="I52" s="3">
-        <v>14700</v>
+        <v>9600</v>
       </c>
       <c r="J52" s="3">
+        <v>9400</v>
+      </c>
+      <c r="K52" s="3">
         <v>10900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6300</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2978,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2911,50 +3034,53 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>540300</v>
+        <v>569300</v>
       </c>
       <c r="E54" s="3">
-        <v>507300</v>
+        <v>541500</v>
       </c>
       <c r="F54" s="3">
-        <v>488300</v>
+        <v>562800</v>
       </c>
       <c r="G54" s="3">
-        <v>512200</v>
+        <v>559900</v>
       </c>
       <c r="H54" s="3">
-        <v>506500</v>
+        <v>570600</v>
       </c>
       <c r="I54" s="3">
-        <v>542500</v>
+        <v>584400</v>
       </c>
       <c r="J54" s="3">
+        <v>596100</v>
+      </c>
+      <c r="K54" s="3">
         <v>539700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>449000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>474000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>485700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>476800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>308500</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2964,8 +3090,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2985,8 +3114,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3006,50 +3136,51 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>25500</v>
+        <v>3300</v>
       </c>
       <c r="E57" s="3">
-        <v>23400</v>
+        <v>3400</v>
       </c>
       <c r="F57" s="3">
-        <v>6300</v>
+        <v>4000</v>
       </c>
       <c r="G57" s="3">
-        <v>10500</v>
+        <v>4500</v>
       </c>
       <c r="H57" s="3">
-        <v>10800</v>
+        <v>3400</v>
       </c>
       <c r="I57" s="3">
-        <v>16800</v>
+        <v>4000</v>
       </c>
       <c r="J57" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K57" s="3">
         <v>19800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24700</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3059,50 +3190,53 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>49900</v>
+      </c>
+      <c r="E58" s="3">
         <v>32800</v>
       </c>
-      <c r="E58" s="3">
-        <v>26800</v>
-      </c>
       <c r="F58" s="3">
-        <v>23500</v>
+        <v>29800</v>
       </c>
       <c r="G58" s="3">
-        <v>43800</v>
+        <v>26900</v>
       </c>
       <c r="H58" s="3">
-        <v>39600</v>
+        <v>48800</v>
       </c>
       <c r="I58" s="3">
-        <v>45600</v>
+        <v>45700</v>
       </c>
       <c r="J58" s="3">
+        <v>50100</v>
+      </c>
+      <c r="K58" s="3">
         <v>46300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>46700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>36800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>34700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>33200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>27900</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3112,50 +3246,53 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>49600</v>
+        <v>34800</v>
       </c>
       <c r="E59" s="3">
-        <v>48900</v>
+        <v>31600</v>
       </c>
       <c r="F59" s="3">
-        <v>52100</v>
+        <v>31400</v>
       </c>
       <c r="G59" s="3">
-        <v>57600</v>
+        <v>18800</v>
       </c>
       <c r="H59" s="3">
-        <v>54600</v>
+        <v>26100</v>
       </c>
       <c r="I59" s="3">
-        <v>69200</v>
+        <v>27000</v>
       </c>
       <c r="J59" s="3">
+        <v>37900</v>
+      </c>
+      <c r="K59" s="3">
         <v>71400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>74800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>70400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>72500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>61000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>56300</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3165,50 +3302,53 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>107800</v>
+        <v>137700</v>
       </c>
       <c r="E60" s="3">
-        <v>99200</v>
+        <v>108000</v>
       </c>
       <c r="F60" s="3">
-        <v>81800</v>
+        <v>110100</v>
       </c>
       <c r="G60" s="3">
-        <v>111800</v>
+        <v>93800</v>
       </c>
       <c r="H60" s="3">
-        <v>104900</v>
+        <v>124600</v>
       </c>
       <c r="I60" s="3">
-        <v>131500</v>
+        <v>121100</v>
       </c>
       <c r="J60" s="3">
+        <v>144500</v>
+      </c>
+      <c r="K60" s="3">
         <v>131200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>138200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>134800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>134500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>110800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>109000</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3218,50 +3358,53 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>126600</v>
+        <v>114200</v>
       </c>
       <c r="E61" s="3">
-        <v>123200</v>
+        <v>126900</v>
       </c>
       <c r="F61" s="3">
-        <v>115300</v>
+        <v>136700</v>
       </c>
       <c r="G61" s="3">
-        <v>116900</v>
+        <v>132300</v>
       </c>
       <c r="H61" s="3">
-        <v>125000</v>
+        <v>130200</v>
       </c>
       <c r="I61" s="3">
-        <v>135100</v>
+        <v>144200</v>
       </c>
       <c r="J61" s="3">
+        <v>148500</v>
+      </c>
+      <c r="K61" s="3">
         <v>142900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>83800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>98200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>119100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>126000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>129600</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3271,50 +3414,53 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F62" s="3">
+        <v>10900</v>
+      </c>
+      <c r="G62" s="3">
+        <v>28900</v>
+      </c>
+      <c r="H62" s="3">
+        <v>29000</v>
+      </c>
+      <c r="I62" s="3">
+        <v>29500</v>
+      </c>
+      <c r="J62" s="3">
+        <v>29200</v>
+      </c>
+      <c r="K62" s="3">
+        <v>30600</v>
+      </c>
+      <c r="L62" s="3">
+        <v>22700</v>
+      </c>
+      <c r="M62" s="3">
+        <v>28000</v>
+      </c>
+      <c r="N62" s="3">
         <v>24600</v>
       </c>
-      <c r="E62" s="3">
-        <v>23800</v>
-      </c>
-      <c r="F62" s="3">
-        <v>37500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>26000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>25500</v>
-      </c>
-      <c r="I62" s="3">
-        <v>26500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>30600</v>
-      </c>
-      <c r="K62" s="3">
-        <v>22700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>28000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>24600</v>
-      </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>20100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20000</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3324,8 +3470,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3377,8 +3526,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3430,8 +3582,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3483,50 +3638,53 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>259000</v>
+        <v>276400</v>
       </c>
       <c r="E66" s="3">
-        <v>246200</v>
+        <v>259600</v>
       </c>
       <c r="F66" s="3">
-        <v>234700</v>
+        <v>273100</v>
       </c>
       <c r="G66" s="3">
-        <v>254800</v>
+        <v>269100</v>
       </c>
       <c r="H66" s="3">
-        <v>255400</v>
+        <v>283800</v>
       </c>
       <c r="I66" s="3">
-        <v>293200</v>
+        <v>294800</v>
       </c>
       <c r="J66" s="3">
+        <v>322200</v>
+      </c>
+      <c r="K66" s="3">
         <v>304600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>244700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>261000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>278200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>257000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>258500</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3536,8 +3694,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3557,8 +3718,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3610,8 +3772,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3663,8 +3828,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3716,8 +3884,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3769,50 +3940,53 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>109400</v>
+        <v>83300</v>
       </c>
       <c r="E72" s="3">
-        <v>99500</v>
+        <v>76600</v>
       </c>
       <c r="F72" s="3">
-        <v>95000</v>
+        <v>75100</v>
       </c>
       <c r="G72" s="3">
-        <v>110300</v>
+        <v>73000</v>
       </c>
       <c r="H72" s="3">
-        <v>102500</v>
+        <v>77700</v>
       </c>
       <c r="I72" s="3">
-        <v>92300</v>
+        <v>73000</v>
       </c>
       <c r="J72" s="3">
+        <v>60100</v>
+      </c>
+      <c r="K72" s="3">
         <v>76400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>45800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>41100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>35100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>27500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>31300</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3822,8 +3996,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3875,8 +4052,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3928,8 +4108,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3981,50 +4164,53 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>281300</v>
+        <v>292900</v>
       </c>
       <c r="E76" s="3">
-        <v>261100</v>
+        <v>281900</v>
       </c>
       <c r="F76" s="3">
-        <v>253600</v>
+        <v>289700</v>
       </c>
       <c r="G76" s="3">
-        <v>257400</v>
+        <v>290800</v>
       </c>
       <c r="H76" s="3">
-        <v>251000</v>
+        <v>286800</v>
       </c>
       <c r="I76" s="3">
-        <v>249300</v>
+        <v>289700</v>
       </c>
       <c r="J76" s="3">
+        <v>273900</v>
+      </c>
+      <c r="K76" s="3">
         <v>235100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>204200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>213000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>207400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>219900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>49900</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4034,8 +4220,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4087,55 +4276,58 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4145,50 +4337,53 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E81" s="3">
         <v>8700</v>
       </c>
-      <c r="E81" s="3">
-        <v>4000</v>
-      </c>
       <c r="F81" s="3">
-        <v>-700</v>
+        <v>4500</v>
       </c>
       <c r="G81" s="3">
-        <v>6500</v>
+        <v>-800</v>
       </c>
       <c r="H81" s="3">
-        <v>7000</v>
+        <v>5400</v>
       </c>
       <c r="I81" s="3">
-        <v>7800</v>
+        <v>8100</v>
       </c>
       <c r="J81" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>7500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-400</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4198,8 +4393,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4219,47 +4417,48 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>4200</v>
+        <v>4900</v>
       </c>
       <c r="E83" s="3">
-        <v>3900</v>
+        <v>2300</v>
       </c>
       <c r="F83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="K83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="L83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="M83" s="3">
+        <v>4900</v>
+      </c>
+      <c r="N83" s="3">
         <v>4000</v>
       </c>
-      <c r="G83" s="3">
-        <v>4100</v>
-      </c>
-      <c r="H83" s="3">
-        <v>4100</v>
-      </c>
-      <c r="I83" s="3">
-        <v>4500</v>
-      </c>
-      <c r="J83" s="3">
-        <v>4900</v>
-      </c>
-      <c r="K83" s="3">
-        <v>4400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>4900</v>
-      </c>
-      <c r="M83" s="3">
-        <v>4000</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>9800</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4272,8 +4471,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4325,8 +4527,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4378,8 +4583,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4431,8 +4639,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4484,8 +4695,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4537,47 +4751,50 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4100</v>
       </c>
-      <c r="E89" s="3">
-        <v>21400</v>
-      </c>
       <c r="F89" s="3">
-        <v>21100</v>
+        <v>23800</v>
       </c>
       <c r="G89" s="3">
-        <v>20800</v>
+        <v>24200</v>
       </c>
       <c r="H89" s="3">
-        <v>-5600</v>
+        <v>23200</v>
       </c>
       <c r="I89" s="3">
-        <v>16700</v>
+        <v>-6400</v>
       </c>
       <c r="J89" s="3">
+        <v>18400</v>
+      </c>
+      <c r="K89" s="3">
         <v>17400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>16400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4590,8 +4807,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4611,35 +4831,36 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-13100</v>
+        <v>-2700</v>
       </c>
       <c r="E91" s="3">
-        <v>-3600</v>
+        <v>-2400</v>
       </c>
       <c r="F91" s="3">
-        <v>-6500</v>
+        <v>-2200</v>
       </c>
       <c r="G91" s="3">
-        <v>-4000</v>
+        <v>-1900</v>
       </c>
       <c r="H91" s="3">
-        <v>-15900</v>
+        <v>-2300</v>
       </c>
       <c r="I91" s="3">
-        <v>-4600</v>
+        <v>-200</v>
       </c>
       <c r="J91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-7200</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
@@ -4655,8 +4876,8 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -4664,8 +4885,11 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4717,8 +4941,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4770,47 +4997,50 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2400</v>
       </c>
-      <c r="E94" s="3">
-        <v>-1400</v>
-      </c>
       <c r="F94" s="3">
-        <v>4800</v>
+        <v>-1600</v>
       </c>
       <c r="G94" s="3">
-        <v>-1700</v>
+        <v>5500</v>
       </c>
       <c r="H94" s="3">
-        <v>9300</v>
+        <v>-1900</v>
       </c>
       <c r="I94" s="3">
+        <v>10700</v>
+      </c>
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-57700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>26500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-304100</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
@@ -4823,8 +5053,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4844,31 +5077,32 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4880,11 +5114,11 @@
         <v>0</v>
       </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-25400</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
@@ -4897,8 +5131,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4950,8 +5187,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5003,8 +5243,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5056,47 +5299,50 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-10500</v>
+        <v>-2800</v>
       </c>
       <c r="E100" s="3">
-        <v>6200</v>
+        <v>-10600</v>
       </c>
       <c r="F100" s="3">
-        <v>-22300</v>
+        <v>6900</v>
       </c>
       <c r="G100" s="3">
-        <v>-11700</v>
+        <v>-25500</v>
       </c>
       <c r="H100" s="3">
-        <v>-21800</v>
+        <v>-13000</v>
       </c>
       <c r="I100" s="3">
-        <v>-4200</v>
+        <v>-25100</v>
       </c>
       <c r="J100" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K100" s="3">
         <v>36600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-15100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-8200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>277800</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5109,44 +5355,47 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-100</v>
+        <v>700</v>
       </c>
       <c r="E101" s="3">
-        <v>500</v>
+        <v>-400</v>
       </c>
       <c r="F101" s="3">
-        <v>-500</v>
+        <v>-200</v>
       </c>
       <c r="G101" s="3">
-        <v>600</v>
+        <v>-1500</v>
       </c>
       <c r="H101" s="3">
-        <v>-300</v>
+        <v>-800</v>
       </c>
       <c r="I101" s="3">
-        <v>-200</v>
+        <v>-1500</v>
       </c>
       <c r="J101" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-1400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3300</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5162,47 +5411,50 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-17200</v>
       </c>
-      <c r="E102" s="3">
-        <v>26700</v>
-      </c>
       <c r="F102" s="3">
-        <v>3100</v>
+        <v>29600</v>
       </c>
       <c r="G102" s="3">
-        <v>8100</v>
+        <v>3600</v>
       </c>
       <c r="H102" s="3">
-        <v>-18400</v>
+        <v>9000</v>
       </c>
       <c r="I102" s="3">
-        <v>11800</v>
+        <v>-21200</v>
       </c>
       <c r="J102" s="3">
+        <v>13000</v>
+      </c>
+      <c r="K102" s="3">
         <v>6100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>300</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5213,6 +5465,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,82 +656,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
@@ -741,53 +741,56 @@
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>106100</v>
+      </c>
+      <c r="E8" s="3">
         <v>114300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>101900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>104400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>107700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>105900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>118600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>120500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>110000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>103300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>105200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>101100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>92200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>75700</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
@@ -797,53 +800,56 @@
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E9" s="3">
         <v>74600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>66600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>71000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>71900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>71400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>77600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>80500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>70300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>67200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>68400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>67700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>59500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>49700</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -853,53 +859,56 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E10" s="3">
         <v>39600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>35300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>33400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>35800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>34500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>41000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>39900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>39700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>36100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>36800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>33500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>32700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>26000</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -909,8 +918,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,8 +943,9 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -942,24 +955,24 @@
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,8 +1000,11 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,8 +1059,11 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1069,27 +1088,27 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M14" s="3">
         <v>-100</v>
       </c>
       <c r="N14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O14" s="3">
         <v>200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1099,35 +1118,38 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2800</v>
+        <v>7200</v>
       </c>
       <c r="E15" s="3">
         <v>2800</v>
       </c>
       <c r="F15" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G15" s="3">
         <v>3000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3600</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1155,8 +1177,11 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,53 +1199,54 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>90900</v>
+      </c>
+      <c r="E17" s="3">
         <v>99900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>88000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>94100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>96500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>92000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>102500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>103900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>94400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>91400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>92900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>88500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>76300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>67900</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1230,53 +1256,56 @@
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E18" s="3">
         <v>14400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>13900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>10300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>7900</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1286,8 +1315,11 @@
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,53 +1340,54 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2000</v>
-      </c>
-      <c r="M20" s="3">
-        <v>300</v>
       </c>
       <c r="N20" s="3">
         <v>300</v>
       </c>
       <c r="O20" s="3">
+        <v>300</v>
+      </c>
+      <c r="P20" s="3">
         <v>5300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>3500</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1364,50 +1397,53 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E21" s="3">
         <v>16400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>17500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>13800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>21000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>19800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>20100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>18100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>18300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>17500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>16900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>31000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1420,53 +1456,56 @@
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E22" s="3">
         <v>3600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>4000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4200</v>
-      </c>
-      <c r="I22" s="3">
-        <v>4400</v>
       </c>
       <c r="J22" s="3">
         <v>4400</v>
       </c>
       <c r="K22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="L22" s="3">
         <v>3400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>8100</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1476,53 +1515,56 @@
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E23" s="3">
         <v>10600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>9900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>9800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>10600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>8800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>9200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3400</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1532,53 +1574,56 @@
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E24" s="3">
         <v>5400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>9800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3800</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1588,8 +1633,11 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,53 +1692,56 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>8100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8600</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>7500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>6000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-400</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1700,53 +1751,56 @@
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>8100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8600</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>7500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>6000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-400</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1756,8 +1810,11 @@
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,8 +1869,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1868,8 +1928,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +1987,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,53 +2046,56 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-300</v>
       </c>
       <c r="N32" s="3">
         <v>-300</v>
       </c>
       <c r="O32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P32" s="3">
         <v>-5300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2036,53 +2105,56 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>8100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8600</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>7500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>6000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-400</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2092,8 +2164,11 @@
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,53 +2223,56 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>8100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8600</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>7500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>6000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-400</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2204,58 +2282,61 @@
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2265,8 +2346,11 @@
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2371,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,53 +2394,54 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>56700</v>
+      </c>
+      <c r="E41" s="3">
         <v>70400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>47700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>71800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>43600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>38900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>31000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>49700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>22900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>12600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>13500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>27400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22800</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2365,8 +2451,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2380,35 +2469,35 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>18500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>27800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>47200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>59000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>97000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>161200</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2421,53 +2510,56 @@
       <c r="T42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>136600</v>
+        <v>123600</v>
       </c>
       <c r="E43" s="3">
+        <v>135800</v>
+      </c>
+      <c r="F43" s="3">
         <v>135400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>120800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>136200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>137800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>148700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>137100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>133000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>129300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>133600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>111100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>98000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>96000</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2477,8 +2569,11 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2503,8 +2598,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2533,52 +2628,55 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5700</v>
+        <v>7400</v>
       </c>
       <c r="E45" s="3">
+        <v>6500</v>
+      </c>
+      <c r="F45" s="3">
         <v>7600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>14200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>12400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8500</v>
-      </c>
-      <c r="O45" s="3">
-        <v>6200</v>
       </c>
       <c r="P45" s="3">
         <v>6200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
+      <c r="Q45" s="3">
+        <v>6200</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
@@ -2589,53 +2687,56 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E46" s="3">
         <v>217300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>194900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>199800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>188000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>199700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>202500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>219500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>192500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>201600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>216100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>230100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>292900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>125000</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,8 +2746,11 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2671,8 +2775,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>700</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>700</v>
@@ -2684,13 +2788,13 @@
         <v>700</v>
       </c>
       <c r="O47" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="P47" s="3">
         <v>600</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
+      <c r="Q47" s="3">
+        <v>600</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
@@ -2701,53 +2805,56 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E48" s="3">
         <v>15500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>19300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>20200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>27000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26400</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2757,53 +2864,56 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>309600</v>
+      </c>
+      <c r="E49" s="3">
         <v>328200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>322900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>337200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>344100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>338600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>347200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>339500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>315600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>207600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>216100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>215900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>149100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>150200</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,8 +2923,11 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +2982,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,53 +3041,56 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>9400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6300</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2981,8 +3100,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,53 +3159,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>527000</v>
+      </c>
+      <c r="E54" s="3">
         <v>569300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>541500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>562800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>559900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>570600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>584400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>596100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>539700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>449000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>474000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>485700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>476800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>308500</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3218,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3243,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,53 +3266,54 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E57" s="3">
         <v>3300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>19800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>27700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>24700</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,53 +3323,56 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E58" s="3">
         <v>49900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>32800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>29800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>26900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>48800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>45700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>50100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>46300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>46700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>36800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>34700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>33200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>27900</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3249,53 +3382,56 @@
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>25600</v>
+      </c>
+      <c r="E59" s="3">
         <v>34800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>31400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>18800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>26100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>27000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>37900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>71400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>74800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>70400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>72500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>61000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>56300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,53 +3441,56 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>125100</v>
+      </c>
+      <c r="E60" s="3">
         <v>137700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>108000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>110100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>93800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>124600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>121100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>144500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>131200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>138200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>134800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>134500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>110800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>109000</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,53 +3500,56 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E61" s="3">
         <v>114200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>126900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>136700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>132300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>130200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>144200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>148500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>142900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>83800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>98200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>119100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>126000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>129600</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3417,53 +3559,56 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E62" s="3">
         <v>8400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>9300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>10900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>28900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>29000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>30600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>28000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>24600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3473,8 +3618,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3677,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3736,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,53 +3795,56 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>246600</v>
+      </c>
+      <c r="E66" s="3">
         <v>276400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>259600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>273100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>269100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>283800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>294800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>322200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>304600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>244700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>261000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>278200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>257000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>258500</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +3854,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +3879,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +3936,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +3995,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,8 +4054,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,8 +4113,11 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3952,44 +4125,44 @@
         <v>83300</v>
       </c>
       <c r="E72" s="3">
+        <v>83300</v>
+      </c>
+      <c r="F72" s="3">
         <v>76600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>75100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>73000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>77700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>73000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>60100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>76400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>45800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>41100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>35100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>27500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>31300</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4172,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4231,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4290,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,53 +4349,56 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>280400</v>
+      </c>
+      <c r="E76" s="3">
         <v>292900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>281900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>289700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>290800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>286800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>289700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>273900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>235100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>204200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>213000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>207400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>219900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>49900</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4408,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,58 +4467,61 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4340,53 +4531,56 @@
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>8100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8600</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>7500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>6000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-400</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4396,8 +4590,11 @@
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,25 +4615,26 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E83" s="3">
         <v>4900</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2300</v>
       </c>
       <c r="F83" s="3">
         <v>2300</v>
       </c>
       <c r="G83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="H83" s="3">
         <v>2400</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2300</v>
       </c>
       <c r="I83" s="3">
         <v>2300</v>
@@ -4445,23 +4643,23 @@
         <v>2300</v>
       </c>
       <c r="K83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L83" s="3">
         <v>4900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>4400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9800</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4474,8 +4672,11 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4731,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4790,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +4849,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +4908,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,50 +4967,53 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E89" s="3">
         <v>27000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>23800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>24200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>23200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>18400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>16400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>26700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4810,8 +5026,11 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,38 +5051,39 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7200</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
@@ -4879,8 +5099,8 @@
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
@@ -4888,8 +5108,11 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5167,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,50 +5226,53 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>5500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>10700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-57700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>26500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-304100</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5056,8 +5285,11 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5310,9 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5104,8 +5337,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5117,11 +5350,11 @@
         <v>0</v>
       </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-25400</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
@@ -5134,8 +5367,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5426,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5485,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,50 +5544,53 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-10600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-25500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-13000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>36600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-15100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-8200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>277800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,47 +5603,50 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E101" s="3">
         <v>700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3300</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5414,50 +5662,53 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E102" s="3">
         <v>21800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>13000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-5500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>300</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,6 +5719,9 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,85 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
@@ -744,56 +745,59 @@
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>106100</v>
+        <v>110900</v>
       </c>
       <c r="E8" s="3">
+        <v>162300</v>
+      </c>
+      <c r="F8" s="3">
         <v>114300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>101900</v>
       </c>
-      <c r="G8" s="3">
-        <v>104400</v>
-      </c>
       <c r="H8" s="3">
-        <v>107700</v>
+        <v>105700</v>
       </c>
       <c r="I8" s="3">
+        <v>94300</v>
+      </c>
+      <c r="J8" s="3">
         <v>105900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>118600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>120500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>110000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>103300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>105200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>101100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>92200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>75700</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
@@ -803,56 +807,59 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>68600</v>
+        <v>76400</v>
       </c>
       <c r="E9" s="3">
+        <v>105700</v>
+      </c>
+      <c r="F9" s="3">
         <v>74600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>66600</v>
-      </c>
-      <c r="G9" s="3">
-        <v>71000</v>
       </c>
       <c r="H9" s="3">
         <v>71900</v>
       </c>
       <c r="I9" s="3">
+        <v>63000</v>
+      </c>
+      <c r="J9" s="3">
         <v>71400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>77600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>80500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>70300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>67200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>68400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>67700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>59500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>49700</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -862,56 +869,59 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>37600</v>
+        <v>34500</v>
       </c>
       <c r="E10" s="3">
+        <v>56600</v>
+      </c>
+      <c r="F10" s="3">
         <v>39600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>35300</v>
       </c>
-      <c r="G10" s="3">
-        <v>33400</v>
-      </c>
       <c r="H10" s="3">
-        <v>35800</v>
+        <v>33800</v>
       </c>
       <c r="I10" s="3">
+        <v>31300</v>
+      </c>
+      <c r="J10" s="3">
         <v>34500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>41000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>39900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>39700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>36100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>36800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>33500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>32700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>26000</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,8 +931,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -944,38 +957,39 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
+      <c r="E12" s="3">
+        <v>-800</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="3">
-        <v>200</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="G12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3">
-        <v>100</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1003,8 +1017,11 @@
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1062,8 +1079,11 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1091,27 +1111,27 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N14" s="3">
         <v>-100</v>
       </c>
       <c r="O14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P14" s="3">
         <v>200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1121,38 +1141,41 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>7200</v>
+        <v>3800</v>
       </c>
       <c r="E15" s="3">
-        <v>2800</v>
+        <v>3400</v>
       </c>
       <c r="F15" s="3">
         <v>2800</v>
       </c>
       <c r="G15" s="3">
-        <v>3000</v>
+        <v>2800</v>
       </c>
       <c r="H15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I15" s="3">
         <v>3200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1180,8 +1203,11 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1200,56 +1226,57 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>90900</v>
+        <v>96700</v>
       </c>
       <c r="E17" s="3">
+        <v>140100</v>
+      </c>
+      <c r="F17" s="3">
         <v>99900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>88000</v>
       </c>
-      <c r="G17" s="3">
-        <v>94100</v>
-      </c>
       <c r="H17" s="3">
-        <v>96500</v>
+        <v>95300</v>
       </c>
       <c r="I17" s="3">
+        <v>85100</v>
+      </c>
+      <c r="J17" s="3">
         <v>92000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>102500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>103900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>94400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>91400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>92900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>88500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>76300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>67900</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1259,56 +1286,59 @@
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>15200</v>
+        <v>14200</v>
       </c>
       <c r="E18" s="3">
+        <v>22100</v>
+      </c>
+      <c r="F18" s="3">
         <v>14400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>13900</v>
       </c>
-      <c r="G18" s="3">
-        <v>10300</v>
-      </c>
       <c r="H18" s="3">
-        <v>11200</v>
+        <v>10400</v>
       </c>
       <c r="I18" s="3">
+        <v>9300</v>
+      </c>
+      <c r="J18" s="3">
         <v>13900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>16600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>11900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7900</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1318,8 +1348,11 @@
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1341,56 +1374,57 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-200</v>
       </c>
       <c r="E20" s="3">
+        <v>16200</v>
+      </c>
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
-        <v>-500</v>
-      </c>
       <c r="H20" s="3">
-        <v>300</v>
+        <v>-400</v>
       </c>
       <c r="I20" s="3">
+        <v>16500</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2000</v>
-      </c>
-      <c r="N20" s="3">
-        <v>300</v>
       </c>
       <c r="O20" s="3">
         <v>300</v>
       </c>
       <c r="P20" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q20" s="3">
         <v>5300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3500</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1400,53 +1434,56 @@
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>22400</v>
+        <v>18100</v>
       </c>
       <c r="E21" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F21" s="3">
         <v>16400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17500</v>
       </c>
-      <c r="G21" s="3">
-        <v>13800</v>
-      </c>
       <c r="H21" s="3">
-        <v>14100</v>
+        <v>15200</v>
       </c>
       <c r="I21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="J21" s="3">
         <v>21000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>20100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>18100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>17500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>16900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>31000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,56 +1496,59 @@
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>7400</v>
+        <v>3300</v>
       </c>
       <c r="E22" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="F22" s="3">
         <v>3600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3400</v>
       </c>
-      <c r="G22" s="3">
-        <v>3500</v>
-      </c>
       <c r="H22" s="3">
-        <v>4000</v>
+        <v>3800</v>
       </c>
       <c r="I22" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="J22" s="3">
         <v>4200</v>
-      </c>
-      <c r="J22" s="3">
-        <v>4400</v>
       </c>
       <c r="K22" s="3">
         <v>4400</v>
       </c>
       <c r="L22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="M22" s="3">
         <v>3400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>8100</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1518,56 +1558,59 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>12000</v>
+        <v>12500</v>
       </c>
       <c r="E23" s="3">
+        <v>17500</v>
+      </c>
+      <c r="F23" s="3">
         <v>10600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11800</v>
       </c>
-      <c r="G23" s="3">
-        <v>7800</v>
-      </c>
       <c r="H23" s="3">
-        <v>7600</v>
+        <v>7900</v>
       </c>
       <c r="I23" s="3">
+        <v>6100</v>
+      </c>
+      <c r="J23" s="3">
         <v>9900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>10600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>3400</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,56 +1620,59 @@
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="E24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="F24" s="3">
         <v>5400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3400</v>
       </c>
-      <c r="H24" s="3">
-        <v>8400</v>
-      </c>
       <c r="I24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J24" s="3">
         <v>4500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3800</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1636,8 +1682,11 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1695,56 +1744,59 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>10000</v>
+        <v>7400</v>
       </c>
       <c r="E26" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F26" s="3">
         <v>5200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4500</v>
       </c>
-      <c r="H26" s="3">
-        <v>-800</v>
-      </c>
       <c r="I26" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J26" s="3">
         <v>5400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8600</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>7500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>8800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-400</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1754,56 +1806,59 @@
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>10000</v>
+        <v>7400</v>
       </c>
       <c r="E27" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F27" s="3">
         <v>5200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4500</v>
       </c>
-      <c r="H27" s="3">
-        <v>-800</v>
-      </c>
       <c r="I27" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J27" s="3">
         <v>5400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8600</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>7500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>5200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>6000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>8800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-400</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1813,8 +1868,11 @@
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1872,8 +1930,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1931,8 +1992,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1990,8 +2054,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2049,56 +2116,59 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>200</v>
       </c>
       <c r="E32" s="3">
+        <v>-16200</v>
+      </c>
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
-        <v>500</v>
-      </c>
       <c r="H32" s="3">
-        <v>-300</v>
+        <v>400</v>
       </c>
       <c r="I32" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-300</v>
       </c>
       <c r="O32" s="3">
         <v>-300</v>
       </c>
       <c r="P32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3500</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2108,56 +2178,59 @@
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>10000</v>
+        <v>7400</v>
       </c>
       <c r="E33" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F33" s="3">
         <v>5200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4500</v>
       </c>
-      <c r="H33" s="3">
-        <v>-800</v>
-      </c>
       <c r="I33" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J33" s="3">
         <v>5400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8600</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>7500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>5200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>6000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>8800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-400</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2167,8 +2240,11 @@
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2226,56 +2302,59 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>10000</v>
+        <v>7400</v>
       </c>
       <c r="E35" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F35" s="3">
         <v>5200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4500</v>
       </c>
-      <c r="H35" s="3">
-        <v>-800</v>
-      </c>
       <c r="I35" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J35" s="3">
         <v>5400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8600</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>7500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>5200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>6000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>8800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-400</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,61 +2364,64 @@
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2349,8 +2431,11 @@
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2372,8 +2457,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2395,56 +2481,57 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>56700</v>
+        <v>62800</v>
       </c>
       <c r="E41" s="3">
+        <v>56600</v>
+      </c>
+      <c r="F41" s="3">
         <v>70400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>47700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>71800</v>
       </c>
-      <c r="H41" s="3">
-        <v>43600</v>
-      </c>
       <c r="I41" s="3">
+        <v>43700</v>
+      </c>
+      <c r="J41" s="3">
         <v>38900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>31000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>49700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>22900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>14500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>12600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>13500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>27400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>22800</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2454,8 +2541,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2463,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2472,35 +2562,35 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J42" s="3">
         <v>7800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>18500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>27800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>47200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>59000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>97000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>161200</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2513,56 +2603,59 @@
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>123600</v>
+        <v>121700</v>
       </c>
       <c r="E43" s="3">
+        <v>123500</v>
+      </c>
+      <c r="F43" s="3">
         <v>135800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>135400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>120800</v>
       </c>
-      <c r="H43" s="3">
-        <v>136200</v>
-      </c>
       <c r="I43" s="3">
+        <v>136500</v>
+      </c>
+      <c r="J43" s="3">
         <v>137800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>148700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>137100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>133000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>129300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>133600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>111100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>98000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>96000</v>
       </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2572,8 +2665,11 @@
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2601,8 +2697,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2631,55 +2727,58 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>7400</v>
+        <v>7800</v>
       </c>
       <c r="E45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="F45" s="3">
         <v>6500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7200</v>
       </c>
-      <c r="H45" s="3">
-        <v>7600</v>
-      </c>
       <c r="I45" s="3">
+        <v>5600</v>
+      </c>
+      <c r="J45" s="3">
         <v>15200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>14200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>12400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>10700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8500</v>
-      </c>
-      <c r="P45" s="3">
-        <v>6200</v>
       </c>
       <c r="Q45" s="3">
         <v>6200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
+      <c r="R45" s="3">
+        <v>6200</v>
       </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
@@ -2690,56 +2789,59 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>192000</v>
+        <v>192300</v>
       </c>
       <c r="E46" s="3">
+        <v>191800</v>
+      </c>
+      <c r="F46" s="3">
         <v>217300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>194900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>199800</v>
       </c>
-      <c r="H46" s="3">
-        <v>188000</v>
-      </c>
       <c r="I46" s="3">
+        <v>188400</v>
+      </c>
+      <c r="J46" s="3">
         <v>199700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>202500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>219500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>192500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>201600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>216100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>230100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>292900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>125000</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2749,8 +2851,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2778,8 +2883,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>700</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>700</v>
@@ -2791,13 +2896,13 @@
         <v>700</v>
       </c>
       <c r="P47" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="Q47" s="3">
         <v>600</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
+      <c r="R47" s="3">
+        <v>600</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
@@ -2808,56 +2913,59 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E48" s="3">
         <v>14000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14100</v>
       </c>
-      <c r="H48" s="3">
-        <v>16100</v>
-      </c>
       <c r="I48" s="3">
+        <v>16200</v>
+      </c>
+      <c r="J48" s="3">
         <v>17000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>27000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26400</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2867,56 +2975,59 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>309600</v>
+        <v>320300</v>
       </c>
       <c r="E49" s="3">
+        <v>309300</v>
+      </c>
+      <c r="F49" s="3">
         <v>328200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>322900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>337200</v>
       </c>
-      <c r="H49" s="3">
-        <v>344100</v>
-      </c>
       <c r="I49" s="3">
+        <v>344900</v>
+      </c>
+      <c r="J49" s="3">
         <v>338600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>347200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>339500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>315600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>207600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>216100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>215900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>149100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>150200</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,8 +3037,11 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2985,8 +3099,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3044,56 +3161,59 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E52" s="3">
         <v>10000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>7800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6300</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3103,8 +3223,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3162,56 +3285,59 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>527000</v>
+        <v>538200</v>
       </c>
       <c r="E54" s="3">
+        <v>526400</v>
+      </c>
+      <c r="F54" s="3">
         <v>569300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>541500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>562800</v>
       </c>
-      <c r="H54" s="3">
-        <v>559900</v>
-      </c>
       <c r="I54" s="3">
+        <v>561200</v>
+      </c>
+      <c r="J54" s="3">
         <v>570600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>584400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>596100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>539700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>449000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>474000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>485700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>476800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>308500</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,8 +3347,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3244,8 +3373,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3267,56 +3397,57 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E57" s="3">
         <v>4800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>19800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>24700</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3326,56 +3457,59 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>52500</v>
+      </c>
+      <c r="F58" s="3">
+        <v>49900</v>
+      </c>
+      <c r="G58" s="3">
+        <v>32800</v>
+      </c>
+      <c r="H58" s="3">
+        <v>29800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>27000</v>
+      </c>
+      <c r="J58" s="3">
+        <v>48800</v>
+      </c>
+      <c r="K58" s="3">
+        <v>45700</v>
+      </c>
+      <c r="L58" s="3">
         <v>50100</v>
       </c>
-      <c r="E58" s="3">
-        <v>49900</v>
-      </c>
-      <c r="F58" s="3">
-        <v>32800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>29800</v>
-      </c>
-      <c r="H58" s="3">
-        <v>26900</v>
-      </c>
-      <c r="I58" s="3">
-        <v>48800</v>
-      </c>
-      <c r="J58" s="3">
-        <v>45700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>50100</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>46300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>46700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>36800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>34700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>33200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>27900</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3385,56 +3519,59 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>25600</v>
+        <v>12300</v>
       </c>
       <c r="E59" s="3">
+        <v>23200</v>
+      </c>
+      <c r="F59" s="3">
         <v>34800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>31600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>31400</v>
       </c>
-      <c r="H59" s="3">
-        <v>18800</v>
-      </c>
       <c r="I59" s="3">
+        <v>22000</v>
+      </c>
+      <c r="J59" s="3">
         <v>26100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>27000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>37900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>71400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>74800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>70400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>72500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>61000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>56300</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3444,56 +3581,59 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>125100</v>
+        <v>123800</v>
       </c>
       <c r="E60" s="3">
+        <v>125000</v>
+      </c>
+      <c r="F60" s="3">
         <v>137700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>108000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>110100</v>
       </c>
-      <c r="H60" s="3">
-        <v>93800</v>
-      </c>
       <c r="I60" s="3">
+        <v>94000</v>
+      </c>
+      <c r="J60" s="3">
         <v>124600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>121100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>144500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>131200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>138200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>134800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>134500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>110800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>109000</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3503,56 +3643,59 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>98100</v>
+      </c>
+      <c r="F61" s="3">
+        <v>114200</v>
+      </c>
+      <c r="G61" s="3">
+        <v>126900</v>
+      </c>
+      <c r="H61" s="3">
+        <v>136700</v>
+      </c>
+      <c r="I61" s="3">
+        <v>132600</v>
+      </c>
+      <c r="J61" s="3">
+        <v>130200</v>
+      </c>
+      <c r="K61" s="3">
+        <v>144200</v>
+      </c>
+      <c r="L61" s="3">
+        <v>148500</v>
+      </c>
+      <c r="M61" s="3">
+        <v>142900</v>
+      </c>
+      <c r="N61" s="3">
+        <v>83800</v>
+      </c>
+      <c r="O61" s="3">
         <v>98200</v>
       </c>
-      <c r="E61" s="3">
-        <v>114200</v>
-      </c>
-      <c r="F61" s="3">
-        <v>126900</v>
-      </c>
-      <c r="G61" s="3">
-        <v>136700</v>
-      </c>
-      <c r="H61" s="3">
-        <v>132300</v>
-      </c>
-      <c r="I61" s="3">
-        <v>130200</v>
-      </c>
-      <c r="J61" s="3">
-        <v>144200</v>
-      </c>
-      <c r="K61" s="3">
-        <v>148500</v>
-      </c>
-      <c r="L61" s="3">
-        <v>142900</v>
-      </c>
-      <c r="M61" s="3">
-        <v>83800</v>
-      </c>
-      <c r="N61" s="3">
-        <v>98200</v>
-      </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>119100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>126000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>129600</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3562,56 +3705,59 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E62" s="3">
         <v>6900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>9300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>10900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>30600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>22700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>28000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>24600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20000</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3621,8 +3767,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3680,8 +3829,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3739,8 +3891,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3798,56 +3953,59 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>246600</v>
+        <v>247400</v>
       </c>
       <c r="E66" s="3">
+        <v>246300</v>
+      </c>
+      <c r="F66" s="3">
         <v>276400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>259600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>273100</v>
       </c>
-      <c r="H66" s="3">
-        <v>269100</v>
-      </c>
       <c r="I66" s="3">
+        <v>269700</v>
+      </c>
+      <c r="J66" s="3">
         <v>283800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>294800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>322200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>304600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>244700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>261000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>278200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>257000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>258500</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3857,8 +4015,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3880,8 +4041,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3939,8 +4101,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3998,8 +4163,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4057,8 +4225,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4116,56 +4287,59 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>105400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>97900</v>
+      </c>
+      <c r="F72" s="3">
         <v>83300</v>
       </c>
-      <c r="E72" s="3">
-        <v>83300</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>76600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>75100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
+        <v>68400</v>
+      </c>
+      <c r="J72" s="3">
+        <v>77700</v>
+      </c>
+      <c r="K72" s="3">
         <v>73000</v>
       </c>
-      <c r="I72" s="3">
-        <v>77700</v>
-      </c>
-      <c r="J72" s="3">
-        <v>73000</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>60100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>76400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>45800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>41100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>35100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>27500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>31300</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4175,8 +4349,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4234,8 +4411,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4293,8 +4473,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4352,56 +4535,59 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>280400</v>
+        <v>290800</v>
       </c>
       <c r="E76" s="3">
+        <v>280100</v>
+      </c>
+      <c r="F76" s="3">
         <v>292900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>281900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>289700</v>
       </c>
-      <c r="H76" s="3">
-        <v>290800</v>
-      </c>
       <c r="I76" s="3">
+        <v>291500</v>
+      </c>
+      <c r="J76" s="3">
         <v>286800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>289700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>273900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>235100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>204200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>213000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>207400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>219900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>49900</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4411,8 +4597,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4470,61 +4659,64 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4534,56 +4726,59 @@
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>10000</v>
+        <v>7400</v>
       </c>
       <c r="E81" s="3">
+        <v>13400</v>
+      </c>
+      <c r="F81" s="3">
         <v>5200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4500</v>
       </c>
-      <c r="H81" s="3">
-        <v>-800</v>
-      </c>
       <c r="I81" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J81" s="3">
         <v>5400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8600</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>7500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>5200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>6000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>8800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-400</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4593,8 +4788,11 @@
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4616,28 +4814,29 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2200</v>
+        <v>4400</v>
       </c>
       <c r="E83" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F83" s="3">
         <v>4900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>2300</v>
       </c>
       <c r="G83" s="3">
         <v>2300</v>
       </c>
       <c r="H83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I83" s="3">
         <v>2400</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2300</v>
       </c>
       <c r="J83" s="3">
         <v>2300</v>
@@ -4646,23 +4845,23 @@
         <v>2300</v>
       </c>
       <c r="L83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M83" s="3">
         <v>4900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>4400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9800</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4675,8 +4874,11 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4734,8 +4936,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4793,8 +4998,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4852,8 +5060,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4911,8 +5122,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4970,53 +5184,56 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>21100</v>
+        <v>17600</v>
       </c>
       <c r="E89" s="3">
+        <v>29600</v>
+      </c>
+      <c r="F89" s="3">
         <v>27000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4100</v>
       </c>
-      <c r="G89" s="3">
-        <v>23800</v>
-      </c>
       <c r="H89" s="3">
-        <v>24200</v>
+        <v>24000</v>
       </c>
       <c r="I89" s="3">
+        <v>22700</v>
+      </c>
+      <c r="J89" s="3">
         <v>23200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>18400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>17400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>16400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>26700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5029,8 +5246,11 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5052,41 +5272,42 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-2900</v>
+        <v>-3000</v>
       </c>
       <c r="E91" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-2700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2200</v>
       </c>
-      <c r="H91" s="3">
-        <v>-1900</v>
-      </c>
       <c r="I91" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="J91" s="3">
         <v>-2300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7200</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
       <c r="N91" s="3">
         <v>0</v>
       </c>
@@ -5102,8 +5323,8 @@
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
@@ -5111,8 +5332,11 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5170,8 +5394,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5229,53 +5456,56 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-2900</v>
+        <v>-3000</v>
       </c>
       <c r="E94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-2700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1600</v>
       </c>
-      <c r="H94" s="3">
-        <v>5500</v>
-      </c>
       <c r="I94" s="3">
+        <v>5100</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>10700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-57700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>26500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>19100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-304100</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5288,8 +5518,11 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5311,8 +5544,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5340,8 +5574,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5353,11 +5587,11 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -5370,8 +5604,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5429,8 +5666,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5488,8 +5728,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5547,53 +5790,56 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-26900</v>
+        <v>-11100</v>
       </c>
       <c r="E100" s="3">
+        <v>-29600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-2800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-10600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6900</v>
       </c>
-      <c r="H100" s="3">
-        <v>-25500</v>
-      </c>
       <c r="I100" s="3">
+        <v>-24100</v>
+      </c>
+      <c r="J100" s="3">
         <v>-13000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-25100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>36600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-15100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-8200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>277800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5606,50 +5852,53 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-600</v>
+        <v>-1000</v>
       </c>
       <c r="E101" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F101" s="3">
         <v>700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3300</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5665,53 +5914,56 @@
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-5300</v>
+        <v>6200</v>
       </c>
       <c r="E102" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="F102" s="3">
         <v>21800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17200</v>
       </c>
-      <c r="G102" s="3">
-        <v>29600</v>
-      </c>
       <c r="H102" s="3">
-        <v>3600</v>
+        <v>28400</v>
       </c>
       <c r="I102" s="3">
+        <v>6400</v>
+      </c>
+      <c r="J102" s="3">
         <v>9000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-21200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>13000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>300</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5722,6 +5974,9 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,89 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -748,59 +749,62 @@
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>117200</v>
+      </c>
+      <c r="E8" s="3">
         <v>110900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>162300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>114300</v>
       </c>
-      <c r="G8" s="3">
-        <v>101900</v>
-      </c>
       <c r="H8" s="3">
+        <v>108500</v>
+      </c>
+      <c r="I8" s="3">
         <v>105700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>94300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>105900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>118600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>120500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>110000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>103300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>105200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>101100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>92200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>75700</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
@@ -810,59 +814,62 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>79500</v>
+      </c>
+      <c r="E9" s="3">
         <v>76400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>105700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>74600</v>
       </c>
-      <c r="G9" s="3">
-        <v>66600</v>
-      </c>
       <c r="H9" s="3">
+        <v>70900</v>
+      </c>
+      <c r="I9" s="3">
         <v>71900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>63000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>71400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>77600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>80500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>70300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>67200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>68400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>67700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>59500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>49700</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -872,59 +879,62 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E10" s="3">
         <v>34500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>56600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>39600</v>
       </c>
-      <c r="G10" s="3">
-        <v>35300</v>
-      </c>
       <c r="H10" s="3">
+        <v>37600</v>
+      </c>
+      <c r="I10" s="3">
         <v>33800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>31300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>34500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>41000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>39900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>39700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>36100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>36800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>33500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>32700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>26000</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -934,8 +944,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -958,20 +971,21 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>-800</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G12" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,12 +1001,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3">
         <v>100</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1020,8 +1034,11 @@
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1082,8 +1099,11 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1114,27 +1134,27 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3">
         <v>-100</v>
       </c>
       <c r="P14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Q14" s="3">
         <v>200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1144,8 +1164,11 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1153,32 +1176,32 @@
         <v>3800</v>
       </c>
       <c r="E15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="F15" s="3">
         <v>3400</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2800</v>
       </c>
       <c r="G15" s="3">
         <v>2800</v>
       </c>
       <c r="H15" s="3">
+        <v>4500</v>
+      </c>
+      <c r="I15" s="3">
         <v>4400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3600</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1206,8 +1229,11 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1227,59 +1253,60 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>101700</v>
+      </c>
+      <c r="E17" s="3">
         <v>96700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>140100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>99900</v>
       </c>
-      <c r="G17" s="3">
-        <v>88000</v>
-      </c>
       <c r="H17" s="3">
+        <v>93700</v>
+      </c>
+      <c r="I17" s="3">
         <v>95300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>85100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>92000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>102500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>103900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>94400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>91400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>92900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>88500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>76300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>67900</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1289,59 +1316,62 @@
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E18" s="3">
         <v>14200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>22100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>14400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>14800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>10400</v>
+      </c>
+      <c r="J18" s="3">
+        <v>9300</v>
+      </c>
+      <c r="K18" s="3">
         <v>13900</v>
       </c>
-      <c r="H18" s="3">
-        <v>10400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J18" s="3">
-        <v>13900</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>16100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>16600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>11900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7900</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1351,8 +1381,11 @@
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1375,59 +1408,60 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>16200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>16500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2000</v>
-      </c>
-      <c r="O20" s="3">
-        <v>300</v>
       </c>
       <c r="P20" s="3">
         <v>300</v>
       </c>
       <c r="Q20" s="3">
+        <v>300</v>
+      </c>
+      <c r="R20" s="3">
         <v>5300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>3500</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1437,56 +1471,59 @@
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E21" s="3">
         <v>18100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>9400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>16400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>20200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>15200</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="K21" s="3">
+        <v>21000</v>
+      </c>
+      <c r="L21" s="3">
+        <v>19800</v>
+      </c>
+      <c r="M21" s="3">
+        <v>20100</v>
+      </c>
+      <c r="N21" s="3">
+        <v>18100</v>
+      </c>
+      <c r="O21" s="3">
+        <v>18300</v>
+      </c>
+      <c r="P21" s="3">
         <v>17500</v>
       </c>
-      <c r="H21" s="3">
-        <v>15200</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="J21" s="3">
-        <v>21000</v>
-      </c>
-      <c r="K21" s="3">
-        <v>19800</v>
-      </c>
-      <c r="L21" s="3">
-        <v>20100</v>
-      </c>
-      <c r="M21" s="3">
-        <v>18100</v>
-      </c>
-      <c r="N21" s="3">
-        <v>18300</v>
-      </c>
-      <c r="O21" s="3">
-        <v>17500</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>16900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>31000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1499,59 +1536,62 @@
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E22" s="3">
         <v>3300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-8300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3600</v>
-      </c>
-      <c r="G22" s="3">
-        <v>3400</v>
       </c>
       <c r="H22" s="3">
         <v>3800</v>
       </c>
       <c r="I22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="J22" s="3">
         <v>-12200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4200</v>
-      </c>
-      <c r="K22" s="3">
-        <v>4400</v>
       </c>
       <c r="L22" s="3">
         <v>4400</v>
       </c>
       <c r="M22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="N22" s="3">
         <v>3400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8100</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1561,59 +1601,62 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E23" s="3">
         <v>12500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10600</v>
       </c>
-      <c r="G23" s="3">
-        <v>11800</v>
-      </c>
       <c r="H23" s="3">
+        <v>12600</v>
+      </c>
+      <c r="I23" s="3">
         <v>7900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>6100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>9900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>12300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>10600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3400</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1623,59 +1666,62 @@
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E24" s="3">
         <v>5000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5400</v>
       </c>
-      <c r="G24" s="3">
-        <v>3000</v>
-      </c>
       <c r="H24" s="3">
+        <v>3300</v>
+      </c>
+      <c r="I24" s="3">
         <v>3400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>9800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3800</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1685,8 +1731,11 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1747,59 +1796,62 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E26" s="3">
         <v>7400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5200</v>
       </c>
-      <c r="G26" s="3">
-        <v>8700</v>
-      </c>
       <c r="H26" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I26" s="3">
         <v>4500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>8100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>8600</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>7500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>8800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-400</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1809,59 +1861,62 @@
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E27" s="3">
         <v>7400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5200</v>
       </c>
-      <c r="G27" s="3">
-        <v>8700</v>
-      </c>
       <c r="H27" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I27" s="3">
         <v>4500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>5400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>8100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>8600</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>7500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>5200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>6000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>8800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-400</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1871,8 +1926,11 @@
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1933,8 +1991,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1995,8 +2056,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2057,8 +2121,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2119,59 +2186,62 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-16200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-16500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-300</v>
       </c>
       <c r="P32" s="3">
         <v>-300</v>
       </c>
       <c r="Q32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R32" s="3">
         <v>-5300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-3500</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2181,59 +2251,62 @@
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E33" s="3">
         <v>7400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5200</v>
       </c>
-      <c r="G33" s="3">
-        <v>8700</v>
-      </c>
       <c r="H33" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I33" s="3">
         <v>4500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>5400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>8100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>8600</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>7500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>5200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>6000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>8800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-400</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2243,8 +2316,11 @@
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2305,59 +2381,62 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E35" s="3">
         <v>7400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5200</v>
       </c>
-      <c r="G35" s="3">
-        <v>8700</v>
-      </c>
       <c r="H35" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I35" s="3">
         <v>4500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>5400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>8100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>8600</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>7500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>5200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>6000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>8800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-400</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2367,64 +2446,67 @@
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2434,8 +2516,11 @@
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2458,8 +2543,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2482,59 +2568,60 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E41" s="3">
         <v>62800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>56600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>70400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>47700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>71800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>43700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>38900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>49700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>22900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>14500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>12600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>13500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>27400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>22800</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2544,20 +2631,23 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>700</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -2565,35 +2655,35 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>2600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>27800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>47200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>59000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>97000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>161200</v>
       </c>
-      <c r="R42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2606,59 +2696,62 @@
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>127800</v>
+      </c>
+      <c r="E43" s="3">
         <v>121700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>123500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>135800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>135400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>120800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>136500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>137800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>148700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>137100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>133000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>129300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>133600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>111100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>98000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>96000</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2668,8 +2761,11 @@
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2700,8 +2796,8 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -2730,58 +2826,61 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E45" s="3">
         <v>7800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>14200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>10700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8500</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>6200</v>
       </c>
       <c r="R45" s="3">
         <v>6200</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
+      <c r="S45" s="3">
+        <v>6200</v>
       </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
@@ -2792,59 +2891,62 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>194500</v>
+      </c>
+      <c r="E46" s="3">
         <v>192300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>191800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>217300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>194900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>199800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>188400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>199700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>202500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>219500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>192500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>201600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>216100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>230100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>292900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>125000</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2854,8 +2956,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2886,8 +2991,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>700</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>700</v>
@@ -2899,13 +3004,13 @@
         <v>700</v>
       </c>
       <c r="Q47" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="R47" s="3">
         <v>600</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
+      <c r="S47" s="3">
+        <v>600</v>
       </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
@@ -2916,59 +3021,62 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E48" s="3">
         <v>13800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>14000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>20200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>20000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>27000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>27500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26400</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2978,59 +3086,62 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>331100</v>
+      </c>
+      <c r="E49" s="3">
         <v>320300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>309300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>328200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>322900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>337200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>344900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>338600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>347200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>339500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>315600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>207600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>216100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>215900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>149100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>150200</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3040,8 +3151,11 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3102,8 +3216,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3164,59 +3281,62 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E52" s="3">
         <v>11100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>10000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6300</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3226,8 +3346,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3288,59 +3411,62 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>552800</v>
+      </c>
+      <c r="E54" s="3">
         <v>538200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>526400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>569300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>541500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>562800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>561200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>570600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>584400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>596100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>539700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>449000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>474000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>485700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>476800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>308500</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3350,8 +3476,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3374,8 +3503,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3398,59 +3528,60 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E57" s="3">
         <v>4600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>19800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>27400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>24700</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3460,59 +3591,62 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E58" s="3">
         <v>54400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>52500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>49900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>32800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>29800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>27000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>48800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>45700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>50100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>46300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>46700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>36800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>34700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>33200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>27900</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3522,59 +3656,62 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E59" s="3">
         <v>12300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>34800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>31600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>31400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>22000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>26100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>27000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>37900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>71400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>74800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>70400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>72500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>61000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>56300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3584,59 +3721,62 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>130900</v>
+      </c>
+      <c r="E60" s="3">
         <v>123800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>125000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>137700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>108000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>110100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>94000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>124600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>121100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>144500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>131200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>138200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>134800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>134500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>110800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>109000</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,59 +3786,62 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E61" s="3">
         <v>95500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>98100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>114200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>126900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>136700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>132600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>130200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>144200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>148500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>142900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>83800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>98200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>119100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>126000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>129600</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -3708,59 +3851,62 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E62" s="3">
         <v>7600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>9300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>28900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>30600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>22700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>28000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>24600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>20100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20000</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3770,8 +3916,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3832,8 +3981,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3894,8 +4046,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3956,59 +4111,62 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>250600</v>
+      </c>
+      <c r="E66" s="3">
         <v>247400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>246300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>276400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>259600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>273100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>269700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>283800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>294800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>322200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>304600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>244700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>261000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>278200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>257000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>258500</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4018,8 +4176,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4042,8 +4203,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4104,8 +4266,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4166,8 +4331,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4228,8 +4396,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4290,59 +4461,62 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>115100</v>
+      </c>
+      <c r="E72" s="3">
         <v>105400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>97900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>83300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>76600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>75100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>68400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>77700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>73000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>60100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>76400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>45800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>41100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>35100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>27500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>31300</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4352,8 +4526,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4414,8 +4591,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4476,8 +4656,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4538,59 +4721,62 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>302200</v>
+      </c>
+      <c r="E76" s="3">
         <v>290800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>280100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>292900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>281900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>289700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>291500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>286800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>289700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>273900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>235100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>204200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>213000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>207400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>219900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>49900</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4600,8 +4786,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4662,64 +4851,67 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4729,59 +4921,62 @@
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E81" s="3">
         <v>7400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5200</v>
       </c>
-      <c r="G81" s="3">
-        <v>8700</v>
-      </c>
       <c r="H81" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I81" s="3">
         <v>4500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>5400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>8100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>8600</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>7500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>5200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>6000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>8800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-400</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4791,8 +4986,11 @@
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4815,31 +5013,32 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E83" s="3">
         <v>4400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2300</v>
       </c>
       <c r="H83" s="3">
         <v>2300</v>
       </c>
       <c r="I83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J83" s="3">
         <v>2400</v>
-      </c>
-      <c r="J83" s="3">
-        <v>2300</v>
       </c>
       <c r="K83" s="3">
         <v>2300</v>
@@ -4848,23 +5047,23 @@
         <v>2300</v>
       </c>
       <c r="M83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="N83" s="3">
         <v>4900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>4900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9800</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -4877,8 +5076,11 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4939,8 +5141,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5001,8 +5206,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5063,8 +5271,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5125,8 +5336,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5187,56 +5401,59 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E89" s="3">
         <v>17600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>29600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>27000</v>
       </c>
-      <c r="G89" s="3">
-        <v>-4100</v>
-      </c>
       <c r="H89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="I89" s="3">
         <v>24000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>22700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>23200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>18400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>16400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>26700</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5249,8 +5466,11 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5273,44 +5493,45 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-3000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2700</v>
       </c>
-      <c r="G91" s="3">
-        <v>-2400</v>
-      </c>
       <c r="H91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7200</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
@@ -5326,8 +5547,8 @@
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
@@ -5335,8 +5556,11 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5397,8 +5621,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5459,56 +5686,59 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2700</v>
       </c>
-      <c r="G94" s="3">
-        <v>-2400</v>
-      </c>
       <c r="H94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="I94" s="3">
         <v>-1600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>5100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>10700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-57700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>26500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>19100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-304100</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5521,8 +5751,11 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5545,8 +5778,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5577,8 +5811,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -5590,11 +5824,11 @@
         <v>0</v>
       </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-25400</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
@@ -5607,8 +5841,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5669,8 +5906,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5731,8 +5971,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5793,56 +6036,59 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-11100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-29600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2800</v>
       </c>
-      <c r="G100" s="3">
-        <v>-10600</v>
-      </c>
       <c r="H100" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="I100" s="3">
         <v>6900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-24100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-13000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-25100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>36600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-15100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>277800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5855,53 +6101,56 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3300</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
@@ -5917,56 +6166,59 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E102" s="3">
         <v>6200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>21800</v>
       </c>
-      <c r="G102" s="3">
-        <v>-17200</v>
-      </c>
       <c r="H102" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="I102" s="3">
         <v>28400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-21200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>300</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5977,6 +6229,9 @@
         <v>3</v>
       </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,97 +656,97 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -756,65 +756,68 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E8" s="3">
         <v>127300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>117200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>110900</v>
       </c>
-      <c r="G8" s="3">
-        <v>162300</v>
-      </c>
       <c r="H8" s="3">
+        <v>112500</v>
+      </c>
+      <c r="I8" s="3">
         <v>112200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>108500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>105700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>94300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>105900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>118600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>120500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>110000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>103300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>105200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>101100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>92200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>75700</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
@@ -824,65 +827,68 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E9" s="3">
         <v>86200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>79500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>76400</v>
       </c>
-      <c r="G9" s="3">
-        <v>105700</v>
-      </c>
       <c r="H9" s="3">
+        <v>72600</v>
+      </c>
+      <c r="I9" s="3">
         <v>73300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>70900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>71900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>63000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>71400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>77600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>80500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>70300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>67200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>68400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>67700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>59500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>49700</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -892,65 +898,68 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>43300</v>
+      </c>
+      <c r="E10" s="3">
         <v>41100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>37700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>34500</v>
       </c>
-      <c r="G10" s="3">
-        <v>56600</v>
-      </c>
       <c r="H10" s="3">
+        <v>39900</v>
+      </c>
+      <c r="I10" s="3">
         <v>38900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>37600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>33800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>31300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>34500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>41000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>39900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>39700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>36100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>36800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>33500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>32700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>26000</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -960,8 +969,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -986,8 +998,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1000,8 +1013,8 @@
       <c r="F12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="3">
-        <v>-800</v>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -1021,12 +1034,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1054,8 +1067,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1122,8 +1138,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1160,27 +1179,27 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="3">
         <v>-100</v>
       </c>
       <c r="R14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1190,47 +1209,50 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E15" s="3">
         <v>5200</v>
-      </c>
-      <c r="E15" s="3">
-        <v>3800</v>
       </c>
       <c r="F15" s="3">
         <v>3800</v>
       </c>
       <c r="G15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="H15" s="3">
         <v>3400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3600</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1258,8 +1280,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1281,65 +1306,66 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E17" s="3">
         <v>109800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>101700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>96700</v>
       </c>
-      <c r="G17" s="3">
-        <v>140100</v>
-      </c>
       <c r="H17" s="3">
+        <v>96300</v>
+      </c>
+      <c r="I17" s="3">
         <v>98100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>93700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>95300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>85100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>92000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>102500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>103900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>94400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>91400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>92900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>88500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>76300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>67900</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1349,65 +1375,68 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E18" s="3">
         <v>17500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>14200</v>
       </c>
-      <c r="G18" s="3">
-        <v>22100</v>
-      </c>
       <c r="H18" s="3">
+        <v>16200</v>
+      </c>
+      <c r="I18" s="3">
         <v>14100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>11900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7900</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1417,8 +1446,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,65 +1475,66 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>1600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
-        <v>16200</v>
-      </c>
       <c r="H20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>16500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2000</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>300</v>
       </c>
       <c r="R20" s="3">
         <v>300</v>
       </c>
       <c r="S20" s="3">
+        <v>300</v>
+      </c>
+      <c r="T20" s="3">
         <v>5300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>3500</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1511,8 +1544,11 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1520,53 +1556,53 @@
         <v>21100</v>
       </c>
       <c r="E21" s="3">
+        <v>21100</v>
+      </c>
+      <c r="F21" s="3">
         <v>20500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>18100</v>
       </c>
-      <c r="G21" s="3">
-        <v>9400</v>
-      </c>
       <c r="H21" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I21" s="3">
         <v>17600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>20200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>15200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-3900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>20100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>18100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>18300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>17500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>16900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>31000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1579,65 +1615,68 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E22" s="3">
         <v>3500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3300</v>
       </c>
-      <c r="G22" s="3">
-        <v>-8300</v>
-      </c>
       <c r="H22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I22" s="3">
         <v>3700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>3800</v>
       </c>
       <c r="J22" s="3">
         <v>3800</v>
       </c>
       <c r="K22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="L22" s="3">
         <v>-12200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>4400</v>
       </c>
       <c r="N22" s="3">
         <v>4400</v>
       </c>
       <c r="O22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="P22" s="3">
         <v>3400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>7000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8100</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1647,65 +1686,68 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E23" s="3">
         <v>13400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>12500</v>
       </c>
-      <c r="G23" s="3">
-        <v>17500</v>
-      </c>
       <c r="H23" s="3">
+        <v>12900</v>
+      </c>
+      <c r="I23" s="3">
         <v>10400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>12600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>9900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>12300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>9800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>8800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>9200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>14300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3400</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1715,65 +1757,68 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>4600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5000</v>
       </c>
-      <c r="G24" s="3">
-        <v>4100</v>
-      </c>
       <c r="H24" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I24" s="3">
         <v>5300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>9800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3800</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1783,8 +1828,11 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1851,65 +1899,68 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E26" s="3">
         <v>8900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>9700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7400</v>
       </c>
-      <c r="G26" s="3">
-        <v>13400</v>
-      </c>
       <c r="H26" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I26" s="3">
         <v>5200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>9300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8600</v>
       </c>
-      <c r="O26" s="3">
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>7500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>5200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>8800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-400</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1919,65 +1970,68 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E27" s="3">
         <v>8900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>9700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7400</v>
       </c>
-      <c r="G27" s="3">
-        <v>13400</v>
-      </c>
       <c r="H27" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I27" s="3">
         <v>5200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>9300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>5400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>8100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8600</v>
       </c>
-      <c r="O27" s="3">
-        <v>0</v>
-      </c>
       <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>7500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>5200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>8800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-400</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1987,8 +2041,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2055,8 +2112,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2123,8 +2183,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2191,8 +2254,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2259,65 +2325,68 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
-        <v>-16200</v>
-      </c>
       <c r="H32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-16500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-300</v>
       </c>
       <c r="R32" s="3">
         <v>-300</v>
       </c>
       <c r="S32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T32" s="3">
         <v>-5300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-3500</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2327,65 +2396,68 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E33" s="3">
         <v>8900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>9700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7400</v>
       </c>
-      <c r="G33" s="3">
-        <v>13400</v>
-      </c>
       <c r="H33" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I33" s="3">
         <v>5200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>9300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>5400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>8100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8600</v>
       </c>
-      <c r="O33" s="3">
-        <v>0</v>
-      </c>
       <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>7500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>5200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>8800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-400</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2395,8 +2467,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2463,65 +2538,68 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E35" s="3">
         <v>8900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>9700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7400</v>
       </c>
-      <c r="G35" s="3">
-        <v>13400</v>
-      </c>
       <c r="H35" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I35" s="3">
         <v>5200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>9300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>5400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>8100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8600</v>
       </c>
-      <c r="O35" s="3">
-        <v>0</v>
-      </c>
       <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>7500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>5200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>8800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-400</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2531,70 +2609,73 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2604,8 +2685,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2630,8 +2714,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2656,65 +2741,66 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E41" s="3">
         <v>43300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>58600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>62800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>56600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>70400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>47700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>71800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>43700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>38900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>49700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>22900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>14500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>12600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>13500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>27400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>22800</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2724,26 +2810,29 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>400</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>700</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
       <c r="I42" s="3">
         <v>0</v>
       </c>
@@ -2751,35 +2840,35 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>2600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>18500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>27800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>47200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>59000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>97000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>161200</v>
       </c>
-      <c r="T42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,65 +2881,68 @@
       <c r="X42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>141700</v>
+      </c>
+      <c r="E43" s="3">
         <v>149100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>127800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>121700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>123500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>135800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>135400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>120800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>136500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>137800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>148700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>137100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>133000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>129300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>133600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>111100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>98000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>96000</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2860,8 +2952,11 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2898,8 +2993,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -2928,64 +3023,67 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E45" s="3">
         <v>7300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>10700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8500</v>
-      </c>
-      <c r="S45" s="3">
-        <v>6200</v>
       </c>
       <c r="T45" s="3">
         <v>6200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
+      <c r="U45" s="3">
+        <v>6200</v>
       </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
@@ -2996,65 +3094,68 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>196100</v>
+      </c>
+      <c r="E46" s="3">
         <v>199800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>194500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>192300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>191800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>217300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>194900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>199800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>188400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>199700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>202500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>219500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>192500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>201600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>216100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>230100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>292900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>125000</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3064,8 +3165,11 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3102,8 +3206,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>700</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>700</v>
@@ -3115,13 +3219,13 @@
         <v>700</v>
       </c>
       <c r="S47" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="T47" s="3">
         <v>600</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
+      <c r="U47" s="3">
+        <v>600</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
@@ -3132,65 +3236,68 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E48" s="3">
         <v>15600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>14000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>15500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>17000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>20200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>27000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26400</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,65 +3307,68 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>329300</v>
+      </c>
+      <c r="E49" s="3">
         <v>333300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>331100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>320300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>309300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>328200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>322900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>337200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>344900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>338600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>347200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>339500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>315600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>207600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>216100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>215900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>149100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>150200</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3268,8 +3378,11 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3336,8 +3449,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3404,65 +3520,68 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E52" s="3">
         <v>5100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6300</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3472,8 +3591,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3540,65 +3662,68 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>550500</v>
+      </c>
+      <c r="E54" s="3">
         <v>554300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>552800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>538200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>526400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>569300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>541500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>562800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>561200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>570600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>584400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>596100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>539700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>449000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>474000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>485700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>476800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>308500</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3608,8 +3733,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3634,8 +3762,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3660,65 +3789,66 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E57" s="3">
         <v>3700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>19800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>27700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>16600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>24700</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3728,65 +3858,68 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E58" s="3">
         <v>73700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>70600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>54400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>52500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>49900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>32800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>29800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>27000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>48800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>45700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>50100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>46300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>46700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>36800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>34700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>33200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>27900</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3796,65 +3929,68 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E59" s="3">
         <v>6400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12300</v>
       </c>
-      <c r="G59" s="3">
-        <v>23200</v>
-      </c>
       <c r="H59" s="3">
+        <v>20100</v>
+      </c>
+      <c r="I59" s="3">
         <v>34800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>31600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>31400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>22000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>26100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>27000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>37900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>71400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>74800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>70400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>72500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>61000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>56300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,65 +4000,68 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>146900</v>
+      </c>
+      <c r="E60" s="3">
         <v>143000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>130900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>123800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>125000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>137700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>108000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>110100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>94000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>124600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>121100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>144500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>131200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>138200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>134800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>134500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>110800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>109000</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,65 +4071,68 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E61" s="3">
         <v>71600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>86900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>95500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>98100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>114200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>126900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>136700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>132600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>130200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>144200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>148500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>142900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>83800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>98200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>119100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>126000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>129600</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4000,65 +4142,68 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E62" s="3">
         <v>8000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>7600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>6900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>9300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>29000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>29200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>30600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>22700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>28000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>24600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>20100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>20000</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4068,8 +4213,11 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4136,8 +4284,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4204,8 +4355,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4272,65 +4426,68 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>241600</v>
+      </c>
+      <c r="E66" s="3">
         <v>248900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>250600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>247400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>246300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>276400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>259600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>273100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>269700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>283800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>294800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>322200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>304600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>244700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>261000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>278200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>257000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>258500</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4340,8 +4497,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4366,8 +4526,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4434,8 +4595,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4502,8 +4666,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4570,8 +4737,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4638,65 +4808,68 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>138500</v>
+      </c>
+      <c r="E72" s="3">
         <v>124000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>115100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>105400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>97900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>83300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>76600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>75100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>68400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>77700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>73000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>60100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>76400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>45800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>41100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>35100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>27500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>31300</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4706,8 +4879,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4774,8 +4950,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4842,8 +5021,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4910,65 +5092,68 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>308900</v>
+      </c>
+      <c r="E76" s="3">
         <v>305400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>302200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>290800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>280100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>292900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>281900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>289700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>291500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>286800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>289700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>273900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>235100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>204200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>213000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>207400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>219900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>49900</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4978,8 +5163,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5046,70 +5234,73 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5119,65 +5310,68 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E81" s="3">
         <v>8900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>9700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7400</v>
       </c>
-      <c r="G81" s="3">
-        <v>13400</v>
-      </c>
       <c r="H81" s="3">
+        <v>10500</v>
+      </c>
+      <c r="I81" s="3">
         <v>5200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>9300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>5400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>8100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8600</v>
       </c>
-      <c r="O81" s="3">
-        <v>0</v>
-      </c>
       <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>7500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>5200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>8800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-400</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5187,8 +5381,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5213,37 +5410,38 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E83" s="3">
         <v>4300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4900</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2300</v>
       </c>
       <c r="J83" s="3">
         <v>2300</v>
       </c>
       <c r="K83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="L83" s="3">
         <v>2400</v>
-      </c>
-      <c r="L83" s="3">
-        <v>2300</v>
       </c>
       <c r="M83" s="3">
         <v>2300</v>
@@ -5252,23 +5450,23 @@
         <v>2300</v>
       </c>
       <c r="O83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="P83" s="3">
         <v>4900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>4400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>9800</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5281,8 +5479,11 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5349,8 +5550,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5417,8 +5621,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5485,8 +5692,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5553,8 +5763,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5621,62 +5834,65 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30100</v>
+      </c>
+      <c r="E89" s="3">
         <v>9200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17600</v>
       </c>
-      <c r="G89" s="3">
-        <v>29600</v>
-      </c>
       <c r="H89" s="3">
+        <v>22600</v>
+      </c>
+      <c r="I89" s="3">
         <v>26600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-4300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>24000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>22700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>23200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>18400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>16400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-15400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>26700</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5689,8 +5905,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5715,50 +5934,51 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-3400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3000</v>
       </c>
-      <c r="G91" s="3">
-        <v>-4200</v>
-      </c>
       <c r="H91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-2700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
@@ -5774,8 +5994,8 @@
       <c r="U91" s="3">
         <v>0</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
+      <c r="V91" s="3">
+        <v>0</v>
       </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
@@ -5783,8 +6003,11 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5851,8 +6074,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5919,62 +6145,65 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3000</v>
       </c>
-      <c r="G94" s="3">
-        <v>-4100</v>
-      </c>
       <c r="H94" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="I94" s="3">
         <v>-2700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>5100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>10700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-57700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>26500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>19100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-304100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5987,8 +6216,11 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6013,8 +6245,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6051,8 +6284,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6064,11 +6297,11 @@
         <v>0</v>
       </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-25400</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
         <v>0</v>
       </c>
@@ -6081,8 +6314,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6149,8 +6385,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6217,8 +6456,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6285,62 +6527,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-24500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-11100</v>
       </c>
-      <c r="G100" s="3">
-        <v>-29600</v>
-      </c>
       <c r="H100" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="I100" s="3">
         <v>-2800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-24100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-13000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-25100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-4600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>36600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-15100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-8200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>277800</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6353,59 +6598,62 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E101" s="3">
         <v>1600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3300</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6421,62 +6669,65 @@
       <c r="X101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-15300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6200</v>
       </c>
-      <c r="G102" s="3">
-        <v>-14900</v>
-      </c>
       <c r="H102" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="I102" s="3">
         <v>22700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-24500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>28400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>13000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>300</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6487,6 +6738,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CINT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
   <si>
     <t>CINT</t>
   </si>
@@ -656,100 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -759,68 +760,71 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>136600</v>
+      </c>
+      <c r="E8" s="3">
         <v>134300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>127300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>117200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>110900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>112500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>112200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>108500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>105700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>94300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>105900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>118600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>120500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>110000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>103300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>105200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>101100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>92200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>75700</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -830,68 +834,71 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>96800</v>
+      </c>
+      <c r="E9" s="3">
         <v>91000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>86200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>79500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>76400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>72600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>73300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>70900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>71900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>63000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>71400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>77600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>80500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>70300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>67200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>68400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>67700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>59500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>49700</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -901,68 +908,71 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E10" s="3">
         <v>43300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>41100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>37700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>34500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>39900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>38900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>37600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>33800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>31300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>34500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>41000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>39900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>39700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>36100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>36800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>33500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>32700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>26000</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,8 +1012,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1037,12 +1051,12 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3">
         <v>100</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1070,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1141,8 +1158,11 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1182,27 +1202,27 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="R14" s="3">
         <v>-100</v>
       </c>
       <c r="S14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1212,50 +1232,53 @@
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E15" s="3">
         <v>2800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>3800</v>
       </c>
       <c r="G15" s="3">
         <v>3800</v>
       </c>
       <c r="H15" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I15" s="3">
         <v>3400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>4400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3600</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1283,8 +1306,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1307,68 +1333,69 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>122400</v>
+      </c>
+      <c r="E17" s="3">
         <v>116000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>109800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>101700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>96700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>96300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>98100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>93700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>95300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>85100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>92000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>102500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>103900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>94400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>91400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>92900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>88500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>76300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>67900</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,68 +1405,71 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>14200</v>
+      </c>
+      <c r="E18" s="3">
         <v>18300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>17500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>15500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>16200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>16600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>11900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>15900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7900</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1449,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,68 +1509,69 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>16500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2000</v>
-      </c>
-      <c r="R20" s="3">
-        <v>300</v>
       </c>
       <c r="S20" s="3">
         <v>300</v>
       </c>
       <c r="T20" s="3">
+        <v>300</v>
+      </c>
+      <c r="U20" s="3">
         <v>5300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3500</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,65 +1581,68 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>21100</v>
+        <v>18500</v>
       </c>
       <c r="E21" s="3">
         <v>21100</v>
       </c>
       <c r="F21" s="3">
+        <v>21100</v>
+      </c>
+      <c r="G21" s="3">
         <v>20500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
+        <v>18800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>18500</v>
+      </c>
+      <c r="J21" s="3">
+        <v>17600</v>
+      </c>
+      <c r="K21" s="3">
+        <v>20200</v>
+      </c>
+      <c r="L21" s="3">
+        <v>15200</v>
+      </c>
+      <c r="M21" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="N21" s="3">
+        <v>21000</v>
+      </c>
+      <c r="O21" s="3">
+        <v>19800</v>
+      </c>
+      <c r="P21" s="3">
+        <v>20100</v>
+      </c>
+      <c r="Q21" s="3">
         <v>18100</v>
       </c>
-      <c r="H21" s="3">
-        <v>18500</v>
-      </c>
-      <c r="I21" s="3">
-        <v>17600</v>
-      </c>
-      <c r="J21" s="3">
-        <v>20200</v>
-      </c>
-      <c r="K21" s="3">
-        <v>15200</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-3900</v>
-      </c>
-      <c r="M21" s="3">
-        <v>21000</v>
-      </c>
-      <c r="N21" s="3">
-        <v>19800</v>
-      </c>
-      <c r="O21" s="3">
-        <v>20100</v>
-      </c>
-      <c r="P21" s="3">
-        <v>18100</v>
-      </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>18300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>17500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>16900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>31000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,68 +1655,71 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E22" s="3">
         <v>3300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>3300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>3400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3700</v>
-      </c>
-      <c r="J22" s="3">
-        <v>3800</v>
       </c>
       <c r="K22" s="3">
         <v>3800</v>
       </c>
       <c r="L22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="M22" s="3">
         <v>-12200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>4400</v>
       </c>
       <c r="O22" s="3">
         <v>4400</v>
       </c>
       <c r="P22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Q22" s="3">
         <v>3400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>7000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8100</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1689,68 +1729,71 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E23" s="3">
         <v>15700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>13400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>12500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>12900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>10400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>12600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>9900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>9800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>8800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>9200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>14300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3400</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1760,68 +1803,71 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>9800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3800</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1831,8 +1877,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1902,68 +1951,71 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E26" s="3">
         <v>14600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>8600</v>
       </c>
-      <c r="P26" s="3">
-        <v>0</v>
-      </c>
       <c r="Q26" s="3">
+        <v>0</v>
+      </c>
+      <c r="R26" s="3">
         <v>7500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>5200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-400</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1973,68 +2025,71 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E27" s="3">
         <v>14600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>9700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>5200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>9300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>5400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>8100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>8600</v>
       </c>
-      <c r="P27" s="3">
-        <v>0</v>
-      </c>
       <c r="Q27" s="3">
+        <v>0</v>
+      </c>
+      <c r="R27" s="3">
         <v>7500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>5200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>8800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-400</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2044,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2115,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2186,8 +2247,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2257,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2328,68 +2395,71 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-16500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2000</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-300</v>
       </c>
       <c r="S32" s="3">
         <v>-300</v>
       </c>
       <c r="T32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U32" s="3">
         <v>-5300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3500</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2399,68 +2469,71 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E33" s="3">
         <v>14600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>9700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>5200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>9300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>5400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>8100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>8600</v>
       </c>
-      <c r="P33" s="3">
-        <v>0</v>
-      </c>
       <c r="Q33" s="3">
+        <v>0</v>
+      </c>
+      <c r="R33" s="3">
         <v>7500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>5200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>8800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-400</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2541,68 +2617,71 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E35" s="3">
         <v>14600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>9700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>5200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>9300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>5400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>8100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>8600</v>
       </c>
-      <c r="P35" s="3">
-        <v>0</v>
-      </c>
       <c r="Q35" s="3">
+        <v>0</v>
+      </c>
+      <c r="R35" s="3">
         <v>7500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>5200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>8800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-400</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2612,73 +2691,76 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2715,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2742,68 +2828,69 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E41" s="3">
         <v>47900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>43300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>58600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>62800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>56600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>70400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>47700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>71800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>43700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>38900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>49700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>22900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>14500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>12600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>13500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>27400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>22800</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2813,29 +2900,32 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>100</v>
+      </c>
+      <c r="E42" s="3">
         <v>200</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>400</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>700</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -2843,35 +2933,35 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>2600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>18500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>27800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>47200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>59000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>97000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>161200</v>
       </c>
-      <c r="U42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2884,68 +2974,71 @@
       <c r="Y42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>154900</v>
+      </c>
+      <c r="E43" s="3">
         <v>141700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>149100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>127800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>121700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>123500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>135800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>135400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>120800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>136500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>137800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>148700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>137100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>133000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>129300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>133600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>111100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>98000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>96000</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2955,8 +3048,11 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2996,8 +3092,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3026,67 +3122,70 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E45" s="3">
         <v>6400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>10700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>10800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8500</v>
-      </c>
-      <c r="T45" s="3">
-        <v>6200</v>
       </c>
       <c r="U45" s="3">
         <v>6200</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
+      <c r="V45" s="3">
+        <v>6200</v>
       </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
@@ -3097,68 +3196,71 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>209900</v>
+      </c>
+      <c r="E46" s="3">
         <v>196100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>199800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>194500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>192300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>191800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>217300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>194900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>199800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>188400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>199700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>202500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>219500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>192500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>201600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>216100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>230100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>292900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>125000</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3168,8 +3270,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3209,8 +3314,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>700</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>700</v>
@@ -3222,13 +3327,13 @@
         <v>700</v>
       </c>
       <c r="T47" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="U47" s="3">
         <v>600</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
+      <c r="V47" s="3">
+        <v>600</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
@@ -3239,68 +3344,71 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E48" s="3">
         <v>14900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>13800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>14000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>17000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>27000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>27500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>26400</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3310,68 +3418,71 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>334900</v>
+      </c>
+      <c r="E49" s="3">
         <v>329300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>333300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>331100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>320300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>309300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>328200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>322900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>337200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>344900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>338600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>347200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>339500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>315600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>207600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>216100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>215900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>149100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>150200</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3381,8 +3492,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3452,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3523,68 +3640,71 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E52" s="3">
         <v>8400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>11100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>10000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>10900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>14100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6300</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,8 +3714,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3665,68 +3788,71 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>568900</v>
+      </c>
+      <c r="E54" s="3">
         <v>550500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>554300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>552800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>538200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>526400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>569300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>541500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>562800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>561200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>570600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>584400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>596100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>539700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>449000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>474000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>485700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>476800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>308500</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3736,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3763,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3790,68 +3920,69 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E57" s="3">
         <v>5200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>4000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>4300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>19800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>27700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>27400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>16600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>24700</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,68 +3992,71 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E58" s="3">
         <v>70400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>73700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>70600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>54400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>52500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>49900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>32800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>29800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>27000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>48800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>45700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>50100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>46300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>46700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>36800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>34700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>33200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>27900</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,68 +4066,71 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E59" s="3">
         <v>9400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>34800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>31600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>31400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>22000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>26100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>37900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>71400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>74800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>70400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>72500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>61000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>56300</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4003,68 +4140,71 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>152800</v>
+      </c>
+      <c r="E60" s="3">
         <v>146900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>143000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>130900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>123800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>125000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>137700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>108000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>110100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>94000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>124600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>121100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>144500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>131200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>138200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>134800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>134500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>110800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>109000</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4074,68 +4214,71 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>58800</v>
+      </c>
+      <c r="E61" s="3">
         <v>61100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>71600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>86900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>95500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>98100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>114200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>126900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>136700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>132600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>130200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>144200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>148500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>142900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>83800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>98200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>119100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>126000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>129600</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4145,68 +4288,71 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E62" s="3">
         <v>7200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>8000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>8100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>7600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>29000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>29500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>29200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>30600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>22700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>28000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>24600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>20100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>20000</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4216,8 +4362,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4287,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4358,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4429,68 +4584,71 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>250300</v>
+      </c>
+      <c r="E66" s="3">
         <v>241600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>248900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>250600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>247400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>246300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>276400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>259600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>273100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>269700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>283800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>294800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>322200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>304600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>244700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>261000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>278200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>257000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>258500</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4527,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4598,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4669,8 +4834,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4740,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4811,68 +4982,71 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>146100</v>
+      </c>
+      <c r="E72" s="3">
         <v>138500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>124000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>115100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>105400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>97900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>83300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>76600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>75100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>68400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>77700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>73000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>60100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>76400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>45800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>41100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>35100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>27500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>31300</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4882,8 +5056,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4953,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5024,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5095,68 +5278,71 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>318600</v>
+      </c>
+      <c r="E76" s="3">
         <v>308900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>305400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>302200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>290800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>280100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>292900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>281900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>289700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>291500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>286800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>289700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>273900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>235100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>204200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>213000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>207400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>219900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>49900</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5166,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5237,73 +5426,76 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5313,68 +5505,71 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E81" s="3">
         <v>14600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>9700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>5200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>9300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>5400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>8100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>8600</v>
       </c>
-      <c r="P81" s="3">
-        <v>0</v>
-      </c>
       <c r="Q81" s="3">
+        <v>0</v>
+      </c>
+      <c r="R81" s="3">
         <v>7500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>5200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>8800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-400</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5384,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5411,40 +5609,41 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E83" s="3">
         <v>2000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>4300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>2300</v>
       </c>
       <c r="K83" s="3">
         <v>2300</v>
       </c>
       <c r="L83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="M83" s="3">
         <v>2400</v>
-      </c>
-      <c r="M83" s="3">
-        <v>2300</v>
       </c>
       <c r="N83" s="3">
         <v>2300</v>
@@ -5453,23 +5652,23 @@
         <v>2300</v>
       </c>
       <c r="P83" s="3">
+        <v>2300</v>
+      </c>
+      <c r="Q83" s="3">
         <v>4900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>4900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>4000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>9800</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5482,8 +5681,11 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5553,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5624,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5695,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5766,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5837,65 +6051,68 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E89" s="3">
         <v>30100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>22600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>26600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>24000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>23200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>18400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>16400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-15400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-15000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>26700</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5908,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5935,53 +6155,54 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-3400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-3000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7200</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -5997,8 +6218,8 @@
       <c r="V91" s="3">
         <v>0</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
+      <c r="W91" s="3">
+        <v>0</v>
       </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
@@ -6006,8 +6227,11 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6077,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6148,65 +6375,68 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-3400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-3100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>5100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>10700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-57700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>26500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>19100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-304100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6219,8 +6449,11 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6246,8 +6479,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6287,8 +6521,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6300,11 +6534,11 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-25400</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -6317,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6388,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6459,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6530,65 +6773,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-20300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-24500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-29000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-11100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-24100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-25100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>36600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-15100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-8200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>277800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6601,62 +6847,65 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>1600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3300</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
@@ -6672,65 +6921,68 @@
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
         <v>4600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-13800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>22700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-24500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>28400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-21200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>13000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>300</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6741,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
